--- a/tame_output/ON/bt/strategyON_20240811.xlsx
+++ b/tame_output/ON/bt/strategyON_20240811.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>110.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.7%</t>
+          <t>430.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-629.6%</t>
+          <t>-620.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.5%</t>
+          <t>-147.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-265.6%</t>
+          <t>-388.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-145.4%</t>
+          <t>-152.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.648745599348358</v>
+        <v>-3.719748766839371</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.261130299208745</v>
+        <v>1.232729032212339</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8375593464264224</v>
+        <v>0.7665561789354089</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.223520571117689</v>
+        <v>3.180918670623081</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.685724627011801</v>
+        <v>-3.756727794502814</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.244748688612615</v>
+        <v>1.21634742161621</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8745332482177529</v>
+        <v>0.8035300807267395</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.244114912661735</v>
+        <v>3.201513012167127</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.527433209472529</v>
+        <v>-3.598436376963542</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.359313020811364</v>
+        <v>1.330911753814958</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8745332482177529</v>
+        <v>0.8035300807267395</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.295362677844774</v>
+        <v>3.252760777350166</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.319791205838053</v>
+        <v>-3.390794373329066</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.440810526859407</v>
+        <v>1.412409259863002</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.082175251852229</v>
+        <v>1.011172084361216</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.418388584619713</v>
+        <v>3.375786684125105</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.268759113115525</v>
+        <v>-3.339762280606538</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.456171592186688</v>
+        <v>1.427770325190283</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.133207344574757</v>
+        <v>1.062204177083744</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.4439560684915</v>
+        <v>3.401354167996892</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.203534931988319</v>
+        <v>-3.274538099479332</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.499448668730276</v>
+        <v>1.47104740173387</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.198431525701963</v>
+        <v>1.127428358210949</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.500277981260528</v>
+        <v>3.45767608076592</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.166107911917185</v>
+        <v>-3.237111079408198</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.510380449058009</v>
+        <v>1.481979182061604</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.203683063731145</v>
+        <v>1.132679896240131</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.499389876377318</v>
+        <v>3.45678797588271</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.186219567951893</v>
+        <v>-3.257222735442907</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.503592578975367</v>
+        <v>1.475191311978961</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.214710408728564</v>
+        <v>1.14370724123755</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.50726307570701</v>
+        <v>3.464661175212401</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.132474753524689</v>
+        <v>-3.203477921015702</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.685648275767459</v>
+        <v>1.657247008771054</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.224773718169026</v>
+        <v>1.153770550678012</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.673858832392498</v>
+        <v>3.63125693189789</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.057692492499676</v>
+        <v>-3.128695659990689</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.835674089395281</v>
+        <v>1.807272822398876</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.299555979194039</v>
+        <v>1.228552811703025</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.838841098225322</v>
+        <v>3.796239197730714</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.031608408235868</v>
+        <v>-3.102611575726881</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.837815699114664</v>
+        <v>1.809414432118258</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.299555979194039</v>
+        <v>1.228552811703025</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.830549074239181</v>
+        <v>3.787947173744573</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.943730495126748</v>
+        <v>-3.014733662617761</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.871160059942091</v>
+        <v>1.842758792945686</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.41548162161739</v>
+        <v>1.344478454126376</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.898297655276972</v>
+        <v>3.855695754782364</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.934838033733464</v>
+        <v>-3.005841201224477</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.892271450226196</v>
+        <v>1.863870183229791</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.41548162161739</v>
+        <v>1.344478454126376</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.915852061003763</v>
+        <v>3.873250160509155</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.103314150703342</v>
+        <v>-3.174317318194355</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.816736050842829</v>
+        <v>1.788334783846424</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.387533785900809</v>
+        <v>1.316530618409795</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.890938406978399</v>
+        <v>3.848336506483791</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.405514621841759</v>
+        <v>-2.476517789332772</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.077125559575324</v>
+        <v>2.048724292578919</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.317185726530398</v>
+        <v>1.246182559039385</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.829999268544014</v>
+        <v>3.787397368049406</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.382793518158606</v>
+        <v>-2.453796685649619</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.07687802354549</v>
+        <v>2.048476756549084</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.317185726530398</v>
+        <v>1.246182559039385</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.820663291040919</v>
+        <v>3.778061390546311</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.511995331452649</v>
+        <v>-2.582998498943662</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.184103424079042</v>
+        <v>2.155702157082636</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.187983913236356</v>
+        <v>1.116980745745342</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.902048328915662</v>
+        <v>3.859446428421054</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.666776338230904</v>
+        <v>-2.737779505721917</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.159268843861386</v>
+        <v>2.130867576864981</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.15461623918188</v>
+        <v>1.083613071690866</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.919105546976623</v>
+        <v>3.876503646482015</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.659721648015731</v>
+        <v>-2.730724815506744</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.158766075937001</v>
+        <v>2.130364808940596</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.161670929397054</v>
+        <v>1.09066776190604</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.920013717095273</v>
+        <v>3.877411816600664</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.632770423689243</v>
+        <v>-2.703773591180256</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.179552719312337</v>
+        <v>2.151151452315932</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.176551275424773</v>
+        <v>1.105548107933759</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.938948078356646</v>
+        <v>3.896346177862037</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.768723431745559</v>
+        <v>-2.839726599236572</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.309274648234771</v>
+        <v>2.280873381238365</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.176551275424773</v>
+        <v>1.105548107933759</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.123051210501606</v>
+        <v>4.080449310006998</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.791131549550431</v>
+        <v>-2.862134717041444</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.292428096015815</v>
+        <v>2.26402682901941</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.176551275424773</v>
+        <v>1.105548107933759</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.115167905404599</v>
+        <v>4.072566004909991</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.819355785128031</v>
+        <v>-2.890358952619045</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.283192401334412</v>
+        <v>2.254791134338007</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.194528027876081</v>
+        <v>1.123524860385068</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.128007956425021</v>
+        <v>4.085406055930413</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.828796711016561</v>
+        <v>-2.899799878507574</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.335669748700847</v>
+        <v>2.307268481704442</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.316955145419473</v>
+        <v>1.245951977928459</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.257717944672903</v>
+        <v>4.215116044178295</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.881070318352203</v>
+        <v>-2.952073485843216</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.317651400311892</v>
+        <v>2.289250133315487</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.264681538083832</v>
+        <v>1.193678370592818</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.229244874816819</v>
+        <v>4.186642974322211</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.957400295953108</v>
+        <v>-3.028403463444122</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.285231222165304</v>
+        <v>2.256829955168899</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.264681538083832</v>
+        <v>1.193678370592818</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.227356687710595</v>
+        <v>4.184754787215986</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.159654016277462</v>
+        <v>-3.230657183768475</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.199149963638425</v>
+        <v>2.17074869664202</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.062427817759478</v>
+        <v>0.9914246502684645</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.100824685118845</v>
+        <v>4.058222784624236</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.321222441804717</v>
+        <v>-3.39222560929573</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.132956603637676</v>
+        <v>2.10455533664127</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9356448939615988</v>
+        <v>0.8646417264705851</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.023188941050269</v>
+        <v>3.980587040555661</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.45352373390227</v>
+        <v>-3.524526901393283</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.093109493664573</v>
+        <v>2.064708226668168</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9356448939615988</v>
+        <v>0.8646417264705851</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.036262347916188</v>
+        <v>3.99366044742158</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.6393920447415</v>
+        <v>-3.710395212232513</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.010767366111821</v>
+        <v>1.982366099115416</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7770793006416511</v>
+        <v>0.7060761331506374</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.933128188707159</v>
+        <v>3.890526288212551</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.667292831850973</v>
+        <v>-3.738295999341986</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.998131092395034</v>
+        <v>1.969729825398629</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7424823764987163</v>
+        <v>0.6714792090077026</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.9108940753484</v>
+        <v>3.868292174853792</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.789818934553867</v>
+        <v>-3.86082210204488</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.945885095291075</v>
+        <v>1.91748382829467</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6199562737958224</v>
+        <v>0.5489531063048088</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.834142857703863</v>
+        <v>3.791540957209254</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.020333430739456</v>
+        <v>-4.091336598230469</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.920385256407343</v>
+        <v>1.891983989410938</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3894417776102337</v>
+        <v>0.31843861011922</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.762540119583013</v>
+        <v>3.719938219088405</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.277054248734279</v>
+        <v>-4.348057416225293</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.958008648211261</v>
+        <v>1.929607381214855</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2810272034664189</v>
+        <v>0.2100240359754052</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.837803094098572</v>
+        <v>3.795201193603963</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.43104066651042</v>
+        <v>-4.502043834001434</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.965394350246445</v>
+        <v>1.936993083250039</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2810272034664189</v>
+        <v>0.2100240359754052</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.906783363244211</v>
+        <v>3.864181462749603</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.380518762682754</v>
+        <v>-4.451521930173768</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.971654313897632</v>
+        <v>1.943253046901226</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2810272034664189</v>
+        <v>0.2100240359754052</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.892834565364332</v>
+        <v>3.850232664869724</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.632993916690478</v>
+        <v>-4.703997084181492</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.882534741349956</v>
+        <v>1.85413347435355</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2810272034664189</v>
+        <v>0.2100240359754052</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.904705054419746</v>
+        <v>3.862103153925138</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.92588967316989</v>
+        <v>-4.996892840660904</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.766586973277135</v>
+        <v>1.738185706280729</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2810272034664189</v>
+        <v>0.2100240359754052</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.90591558893869</v>
+        <v>3.863313688444082</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.083433744899332</v>
+        <v>-5.154436912390346</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.70769108681268</v>
+        <v>1.679289819816274</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2141253983261444</v>
+        <v>0.1431222308351307</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.869896248081846</v>
+        <v>3.827294347587238</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.361398140482605</v>
+        <v>-5.43240130797362</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.59158318131556</v>
+        <v>1.563181914319154</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1245056640406601</v>
+        <v>0.05350249654964645</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.811202260246746</v>
+        <v>3.768600359752137</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.478365833121496</v>
+        <v>-5.54936900061251</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.707000160959047</v>
+        <v>1.678598893962642</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1245056640406601</v>
+        <v>0.05350249654964645</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.973406316945789</v>
+        <v>3.930804416451181</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.56308377534245</v>
+        <v>-5.634086942833464</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.66795962203448</v>
+        <v>1.639558355038075</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.03938963511261373</v>
+        <v>-0.03161353237839992</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.917183337552776</v>
+        <v>3.874581437058167</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.645018593611333</v>
+        <v>-5.716021761102347</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.645415112295418</v>
+        <v>1.617013845299013</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.02945488952553355</v>
+        <v>-0.04154827796548011</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.921451907769019</v>
+        <v>3.878850007274411</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.74699471585974</v>
+        <v>-5.817997883350754</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.613550301851958</v>
+        <v>1.585149034855552</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.07252123272287403</v>
+        <v>-0.1435244002138877</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.869191872875877</v>
+        <v>3.826589972381269</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.636988432382519</v>
+        <v>-5.707991599873533</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.649705702487021</v>
+        <v>1.621304435490616</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.04931666080559882</v>
+        <v>-0.1203198282966125</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.875267503270417</v>
+        <v>3.832665602775809</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.493928856641594</v>
+        <v>-5.564932024132608</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.711179543505366</v>
+        <v>1.682778276508961</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.04130323421561954</v>
+        <v>-0.1123064017066332</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.884325569946379</v>
+        <v>3.841723669451771</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.192482131169756</v>
+        <v>-5.26348529866077</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.839019116576637</v>
+        <v>1.810617849580231</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2601434912562177</v>
+        <v>0.1891403237652041</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.072454488112018</v>
+        <v>4.029852587617409</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.21707237540494</v>
+        <v>-5.288075542895954</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.830154196635274</v>
+        <v>1.801752929638869</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2601434912562177</v>
+        <v>0.1891403237652041</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.073425665864728</v>
+        <v>4.03082376537012</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.16603399939842</v>
+        <v>-5.237037166889434</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.851412451417637</v>
+        <v>1.823011184421232</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2601434912562177</v>
+        <v>0.1891403237652041</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.074268570244484</v>
+        <v>4.031666669749875</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.124894704531789</v>
+        <v>-5.195897872022803</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.886906268238435</v>
+        <v>1.858505001242029</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3012827861228485</v>
+        <v>0.2302796186318349</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.117990246038607</v>
+        <v>4.075388345543999</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.014288564452187</v>
+        <v>-5.085291731943201</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.74733272039421</v>
+        <v>1.718931453397805</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4118889262024505</v>
+        <v>0.3408857587114369</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.000537926210303</v>
+        <v>3.957936025715695</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.144869298983029</v>
+        <v>-5.215872466474043</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.698602470655837</v>
+        <v>1.670201203659432</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.281308191671608</v>
+        <v>0.2103050241805944</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.925691529565762</v>
+        <v>3.883089629071153</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.980372964792068</v>
+        <v>-5.051376132283082</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.748827823408304</v>
+        <v>1.720426556411899</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.281308191671608</v>
+        <v>0.2103050241805944</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.910118348641844</v>
+        <v>3.867516448147235</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.0077428974765</v>
+        <v>-5.078746064967514</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.737067560770961</v>
+        <v>1.708666293774555</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.281308191671608</v>
+        <v>0.2103050241805944</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.909306059078273</v>
+        <v>3.866704158583665</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.018128092366389</v>
+        <v>-5.089131259857403</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.742782261940078</v>
+        <v>1.714380994943672</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2709229967817187</v>
+        <v>0.1999198292907051</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.912943721269412</v>
+        <v>3.870341820774804</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.036716251088614</v>
+        <v>-5.107719418579628</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.806184004227613</v>
+        <v>1.777782737231207</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2523348380594934</v>
+        <v>0.1813316705684797</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.972627831812503</v>
+        <v>3.930025931317894</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.03701479778465</v>
+        <v>-5.108017965275664</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.802933596367497</v>
+        <v>1.774532329371092</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2523348380594934</v>
+        <v>0.1813316705684797</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.969496842630801</v>
+        <v>3.926894942136192</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.936191664094222</v>
+        <v>-5.007194831585236</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.84779374478306</v>
+        <v>1.819392477786654</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2647990535438472</v>
+        <v>0.1937958860528335</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.981506266860804</v>
+        <v>3.938904366366196</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.745410303341815</v>
+        <v>-4.816413470832829</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.924235542562566</v>
+        <v>1.89583427556616</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4555804142962546</v>
+        <v>0.3845772468052409</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.096104336790792</v>
+        <v>4.053502436296184</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.726893449299995</v>
+        <v>-4.797896616791009</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.911479129916891</v>
+        <v>1.883077862920485</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4685105437214628</v>
+        <v>0.3975073762304491</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.083699260183513</v>
+        <v>4.041097359688905</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.701700264798677</v>
+        <v>-4.772703432289691</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.956523340329476</v>
+        <v>1.92812207333307</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4937037282227812</v>
+        <v>0.4227005607317675</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.133782107496363</v>
+        <v>4.091180207001755</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.689646137885714</v>
+        <v>-4.760649305376728</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.955031558996099</v>
+        <v>1.926630291999693</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.505757855135744</v>
+        <v>0.4347546876447303</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.134701151545578</v>
+        <v>4.09209925105097</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.696269384576072</v>
+        <v>-4.767272552067086</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.954262890504092</v>
+        <v>1.925861623507686</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4991346084453856</v>
+        <v>0.4281314409543719</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.132607833715499</v>
+        <v>4.090005933220891</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.593388795047479</v>
+        <v>-4.664391962538494</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.008266152193411</v>
+        <v>1.979864885197006</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6020151979739785</v>
+        <v>0.5310120304829649</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.207187213310537</v>
+        <v>4.164585312815929</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.616830834227566</v>
+        <v>-4.68783400171858</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.01909200669497</v>
+        <v>1.990690739698565</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6020151979739785</v>
+        <v>0.5310120304829649</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.227389883484132</v>
+        <v>4.184787982989524</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.634903342519178</v>
+        <v>-4.705906510010192</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.011863003378326</v>
+        <v>1.98346173638192</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6020151979739785</v>
+        <v>0.5310120304829649</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.227389883484132</v>
+        <v>4.184787982989524</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.86607713639581</v>
+        <v>-4.937080303886824</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.87964539942114</v>
+        <v>1.851244132424734</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6020151979739785</v>
+        <v>0.5310120304829649</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.187641797077599</v>
+        <v>4.14503989658299</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.834791115855355</v>
+        <v>-4.905794283346369</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.899182426634262</v>
+        <v>1.870781159637856</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6333012185144339</v>
+        <v>0.5622980510234202</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.213436028398812</v>
+        <v>4.170834127904204</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.68176572374207</v>
+        <v>-4.752768891233084</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.05956358305248</v>
+        <v>2.031162316056074</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.786326610627718</v>
+        <v>0.7153234431367044</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.404422263239686</v>
+        <v>4.361820362745078</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.851855561383662</v>
+        <v>3.744146567764598</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.68026895671161</v>
+        <v>-4.591116686709011</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.247628514772956</v>
+        <v>2.283289422773996</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.786326610627718</v>
+        <v>0.7153234431367044</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.591888488147979</v>
+        <v>4.549286587653371</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240811.xlsx
+++ b/tame_output/ON/bt/strategyON_20240811.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.1%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.5%</t>
+          <t>430.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-620.7%</t>
+          <t>-637.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-147.9%</t>
+          <t>-154.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-388.8%</t>
+          <t>-305.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.5%</t>
+          <t>-141.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.318354684306547</v>
+        <v>-4.38612833436817</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.129794634852355</v>
+        <v>1.102685174827706</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3554704155919755</v>
+        <v>0.3968615895719985</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.070775182243906</v>
+        <v>3.09560988663192</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.273550512766617</v>
+        <v>-4.34132416282824</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.153724833865253</v>
+        <v>1.126615373840604</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3554704155919755</v>
+        <v>0.3968615895719985</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.076783712640832</v>
+        <v>3.101618417028846</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.125807542531614</v>
+        <v>-4.193581192593237</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.110772243236454</v>
+        <v>1.083662783211804</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5232777728268586</v>
+        <v>0.5646689468068817</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.075418348258962</v>
+        <v>3.100253052646976</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.209628763806313</v>
+        <v>-4.277402413867936</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.080037376258055</v>
+        <v>1.052927916233406</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5232777728268586</v>
+        <v>0.5646689468068817</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.078211969790443</v>
+        <v>3.103046674178457</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.203476057753528</v>
+        <v>-4.271249707815151</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.083160807070827</v>
+        <v>1.056051347046178</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5294304788796429</v>
+        <v>0.570821652859666</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.082565941813772</v>
+        <v>3.107400646201786</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.22028535590403</v>
+        <v>-4.288059005965653</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.075517564550737</v>
+        <v>1.048408104526088</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5126211807291412</v>
+        <v>0.5540123547091644</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.071560839663581</v>
+        <v>3.096395544051595</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.157987357127908</v>
+        <v>-4.225761007189531</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.166772317858007</v>
+        <v>1.139662857833357</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5579154450035833</v>
+        <v>0.5993066189836065</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.165072952025067</v>
+        <v>3.189907656413081</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.95619715946275</v>
+        <v>-4.023970809524373</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.049780398638197</v>
+        <v>1.022670938613548</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7559336371727376</v>
+        <v>0.7973248111527609</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.086175869040687</v>
+        <v>3.111010573428701</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.007083872148945</v>
+        <v>-4.074857522210568</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.099715945885894</v>
+        <v>1.072606485861245</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7050469244865432</v>
+        <v>0.7464380984665664</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.125934073751146</v>
+        <v>3.15076877813916</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.920473129499138</v>
+        <v>-3.988246779560761</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.148987979061861</v>
+        <v>1.121878519037211</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7836726556917014</v>
+        <v>0.8250638296717246</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.187737248590284</v>
+        <v>3.212571952978298</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.980682427504422</v>
+        <v>-4.048456077566045</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.123440240684419</v>
+        <v>1.096330780659769</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7234633576864169</v>
+        <v>0.7648545316664401</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.150147650611785</v>
+        <v>3.174982354999799</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.904260381072495</v>
+        <v>-3.972034031134118</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.152500677297118</v>
+        <v>1.125391217272468</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7234633576864169</v>
+        <v>0.7648545316664401</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.148639268651714</v>
+        <v>3.173473973039727</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.859887249433926</v>
+        <v>-3.92766089949555</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.170112797387981</v>
+        <v>1.143003337363332</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7678364893249855</v>
+        <v>0.8092276633050087</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.175126015070291</v>
+        <v>3.199960719458305</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.882367600292811</v>
+        <v>-3.950141250354434</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.155514451183018</v>
+        <v>1.128404991158369</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7678364893249855</v>
+        <v>0.8092276633050087</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.169519809208881</v>
+        <v>3.194354513596895</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.834711869731755</v>
+        <v>-3.902485519793379</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.180958500435245</v>
+        <v>1.153849040410596</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8154922198860411</v>
+        <v>0.8568833938660644</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.20449500457332</v>
+        <v>3.229329708961333</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.734193711233001</v>
+        <v>-3.801967361294624</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.226058137209472</v>
+        <v>1.198948677184823</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9160103783847957</v>
+        <v>0.9574015523648189</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.269698273047297</v>
+        <v>3.294532977435311</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.718288381800648</v>
+        <v>-3.786062031862271</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.219174941458285</v>
+        <v>1.192065481433636</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8368977176755568</v>
+        <v>0.87828889165558</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.208985349097626</v>
+        <v>3.23382005348564</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.67344998019225</v>
+        <v>-3.741223630253873</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.241208004712273</v>
+        <v>1.214098544687624</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8414411506204262</v>
+        <v>0.8828323246004495</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.215809111475176</v>
+        <v>3.24064381586319</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.692948436434258</v>
+        <v>-3.760722086495881</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.237569561846547</v>
+        <v>1.210460101821898</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7933565093405219</v>
+        <v>0.8347476833205452</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.191119266338311</v>
+        <v>3.215953970726325</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.719748766839371</v>
+        <v>-3.716519249409981</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.232729032212339</v>
+        <v>1.234020839184096</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7665561789354089</v>
+        <v>0.8789505204064456</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.180918670623081</v>
+        <v>3.248355275505703</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.756727794502814</v>
+        <v>-3.753498277073424</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.21634742161621</v>
+        <v>1.217639228587966</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8035300807267395</v>
+        <v>0.9159244221977761</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.201513012167127</v>
+        <v>3.268949617049749</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.598436376963542</v>
+        <v>-3.595206859534152</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.330911753814958</v>
+        <v>1.332203560786714</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8035300807267395</v>
+        <v>0.9159244221977761</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.252760777350166</v>
+        <v>3.320197382232788</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.390794373329066</v>
+        <v>-3.387564855899676</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.412409259863002</v>
+        <v>1.413701066834758</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.011172084361216</v>
+        <v>1.123566425832252</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.375786684125105</v>
+        <v>3.443223289007727</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.339762280606538</v>
+        <v>-3.336532763177148</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.427770325190283</v>
+        <v>1.429062132162039</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.062204177083744</v>
+        <v>1.17459851855478</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.401354167996892</v>
+        <v>3.468790772879514</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.274538099479332</v>
+        <v>-3.271308582049942</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.47104740173387</v>
+        <v>1.472339208705626</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.127428358210949</v>
+        <v>1.239822699681986</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.45767608076592</v>
+        <v>3.525112685648542</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.237111079408198</v>
+        <v>-3.233881561978808</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.481979182061604</v>
+        <v>1.48327098903336</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.132679896240131</v>
+        <v>1.245074237711168</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.45678797588271</v>
+        <v>3.524224580765332</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.257222735442907</v>
+        <v>-3.253993218013516</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.475191311978961</v>
+        <v>1.476483118950717</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.14370724123755</v>
+        <v>1.256101582708587</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.464661175212401</v>
+        <v>3.532097780095024</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.203477921015702</v>
+        <v>-3.200248403586312</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.657247008771054</v>
+        <v>1.65853881574281</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.153770550678012</v>
+        <v>1.266164892149049</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.63125693189789</v>
+        <v>3.698693536780512</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.128695659990689</v>
+        <v>-3.125466142561299</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.807272822398876</v>
+        <v>1.808564629370632</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.228552811703025</v>
+        <v>1.340947153174062</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.796239197730714</v>
+        <v>3.863675802613336</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.102611575726881</v>
+        <v>-3.099382058297491</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.809414432118258</v>
+        <v>1.810706239090014</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.228552811703025</v>
+        <v>1.340947153174062</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.787947173744573</v>
+        <v>3.855383778627195</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.014733662617761</v>
+        <v>-3.011504145188371</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.842758792945686</v>
+        <v>1.844050599917442</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.344478454126376</v>
+        <v>1.456872795597413</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.855695754782364</v>
+        <v>3.923132359664986</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.005841201224477</v>
+        <v>-3.002611683795087</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.863870183229791</v>
+        <v>1.865161990201547</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.344478454126376</v>
+        <v>1.456872795597413</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.873250160509155</v>
+        <v>3.940686765391777</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.174317318194355</v>
+        <v>-3.171087800764965</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.788334783846424</v>
+        <v>1.78962659081818</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.316530618409795</v>
+        <v>1.428924959880832</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.848336506483791</v>
+        <v>3.915773111366413</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.476517789332772</v>
+        <v>-2.473288271903382</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.048724292578919</v>
+        <v>2.050016099550675</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.246182559039385</v>
+        <v>1.358576900510422</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.787397368049406</v>
+        <v>3.854833972932028</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.453796685649619</v>
+        <v>-2.450567168220229</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.048476756549084</v>
+        <v>2.04976856352084</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.246182559039385</v>
+        <v>1.358576900510422</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.778061390546311</v>
+        <v>3.845497995428933</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.582998498943662</v>
+        <v>-2.579768981514272</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.155702157082636</v>
+        <v>2.156993964054393</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.116980745745342</v>
+        <v>1.229375087216379</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.859446428421054</v>
+        <v>3.926883033303676</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.737779505721917</v>
+        <v>-2.734549988292527</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.130867576864981</v>
+        <v>2.132159383836737</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.083613071690866</v>
+        <v>1.196007413161903</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.876503646482015</v>
+        <v>3.943940251364637</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.730724815506744</v>
+        <v>-2.727495298077354</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.130364808940596</v>
+        <v>2.131656615912351</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.09066776190604</v>
+        <v>1.203062103377077</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.877411816600664</v>
+        <v>3.944848421483287</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.703773591180256</v>
+        <v>-2.700544073750866</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.151151452315932</v>
+        <v>2.152443259287688</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.105548107933759</v>
+        <v>1.217942449404796</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.896346177862037</v>
+        <v>3.963782782744659</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.839726599236572</v>
+        <v>-2.836497081807182</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.280873381238365</v>
+        <v>2.282165188210121</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.105548107933759</v>
+        <v>1.217942449404796</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.080449310006998</v>
+        <v>4.14788591488962</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.862134717041444</v>
+        <v>-2.858905199612054</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.26402682901941</v>
+        <v>2.265318635991166</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.105548107933759</v>
+        <v>1.217942449404796</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.072566004909991</v>
+        <v>4.140002609792613</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.890358952619045</v>
+        <v>-2.887129435189654</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.254791134338007</v>
+        <v>2.256082941309763</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.123524860385068</v>
+        <v>1.235919201856105</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.085406055930413</v>
+        <v>4.152842660813035</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.899799878507574</v>
+        <v>-2.896570361078184</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.307268481704442</v>
+        <v>2.308560288676198</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.245951977928459</v>
+        <v>1.358346319399496</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.215116044178295</v>
+        <v>4.282552649060917</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.952073485843216</v>
+        <v>-2.948843968413826</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.289250133315487</v>
+        <v>2.290541940287242</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.193678370592818</v>
+        <v>1.306072712063855</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.186642974322211</v>
+        <v>4.254079579204833</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.028403463444122</v>
+        <v>-3.025173946014732</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.256829955168899</v>
+        <v>2.258121762140656</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.193678370592818</v>
+        <v>1.306072712063855</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.184754787215986</v>
+        <v>4.252191392098609</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.230657183768475</v>
+        <v>-3.227427666339085</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.17074869664202</v>
+        <v>2.172040503613776</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9914246502684645</v>
+        <v>1.103818991739501</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.058222784624236</v>
+        <v>4.125659389506859</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.39222560929573</v>
+        <v>-3.38899609186634</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.10455533664127</v>
+        <v>2.105847143613027</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8646417264705851</v>
+        <v>0.977036067941622</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.980587040555661</v>
+        <v>4.048023645438283</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.524526901393283</v>
+        <v>-3.521297383963893</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.064708226668168</v>
+        <v>2.066000033639924</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8646417264705851</v>
+        <v>0.977036067941622</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.99366044742158</v>
+        <v>4.061097052304202</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.710395212232513</v>
+        <v>-3.707165694803123</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.982366099115416</v>
+        <v>1.983657906087172</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7060761331506374</v>
+        <v>0.8184704746216743</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.890526288212551</v>
+        <v>3.957962893095173</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.738295999341986</v>
+        <v>-3.735066481912596</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.969729825398629</v>
+        <v>1.971021632370385</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6714792090077026</v>
+        <v>0.7838735504787395</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.868292174853792</v>
+        <v>3.935728779736414</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.86082210204488</v>
+        <v>-3.85759258461549</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.91748382829467</v>
+        <v>1.918775635266426</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5489531063048088</v>
+        <v>0.6613474477758456</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.791540957209254</v>
+        <v>3.858977562091877</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.091336598230469</v>
+        <v>-4.088107080801079</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.891983989410938</v>
+        <v>1.893275796382694</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.31843861011922</v>
+        <v>0.4308329515902569</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.719938219088405</v>
+        <v>3.787374823971027</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.348057416225293</v>
+        <v>-4.344827898795902</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.929607381214855</v>
+        <v>1.930899188186612</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2100240359754052</v>
+        <v>0.3224183774464421</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.795201193603963</v>
+        <v>3.862637798486586</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.502043834001434</v>
+        <v>-4.498814316572043</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.936993083250039</v>
+        <v>1.938284890221795</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2100240359754052</v>
+        <v>0.3224183774464421</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.864181462749603</v>
+        <v>3.931618067632225</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.451521930173768</v>
+        <v>-4.448292412744377</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.943253046901226</v>
+        <v>1.944544853872983</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2100240359754052</v>
+        <v>0.3224183774464421</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.850232664869724</v>
+        <v>3.917669269752346</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.703997084181492</v>
+        <v>-4.700767566752101</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.85413347435355</v>
+        <v>1.855425281325307</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2100240359754052</v>
+        <v>0.3224183774464421</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.862103153925138</v>
+        <v>3.92953975880776</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.996892840660904</v>
+        <v>-4.993663323231513</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.738185706280729</v>
+        <v>1.739477513252486</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2100240359754052</v>
+        <v>0.3224183774464421</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.863313688444082</v>
+        <v>3.930750293326704</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.154436912390346</v>
+        <v>-5.151207394960955</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.679289819816274</v>
+        <v>1.68058162678803</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1431222308351307</v>
+        <v>0.2555165723061676</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.827294347587238</v>
+        <v>3.89473095246986</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.43240130797362</v>
+        <v>-5.429171790544228</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.563181914319154</v>
+        <v>1.564473721290911</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.05350249654964645</v>
+        <v>0.1658968380206833</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.768600359752137</v>
+        <v>3.83603696463476</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.54936900061251</v>
+        <v>-5.546139483183119</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.678598893962642</v>
+        <v>1.679890700934398</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.05350249654964645</v>
+        <v>0.1658968380206833</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.930804416451181</v>
+        <v>3.998241021333803</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.634086942833464</v>
+        <v>-5.630857425404073</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.639558355038075</v>
+        <v>1.640850162009831</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.03161353237839992</v>
+        <v>0.08078080909263696</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.874581437058167</v>
+        <v>3.94201804194079</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.716021761102347</v>
+        <v>-5.712792243672956</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.617013845299013</v>
+        <v>1.618305652270769</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.04154827796548011</v>
+        <v>0.07084606350555678</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.878850007274411</v>
+        <v>3.946286612157033</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.817997883350754</v>
+        <v>-5.814768365921363</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.585149034855552</v>
+        <v>1.586440841827308</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1435244002138877</v>
+        <v>-0.0311300587428508</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.826589972381269</v>
+        <v>3.894026577263891</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.707991599873533</v>
+        <v>-5.704762082444142</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.621304435490616</v>
+        <v>1.622596242462373</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1203198282966125</v>
+        <v>-0.007925486825575589</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.832665602775809</v>
+        <v>3.900102207658431</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.564932024132608</v>
+        <v>-5.561702506703217</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.682778276508961</v>
+        <v>1.684070083480717</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1123064017066332</v>
+        <v>8.793976440368834e-05</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.841723669451771</v>
+        <v>3.909160274334393</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.26348529866077</v>
+        <v>-5.260255781231379</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.810617849580231</v>
+        <v>1.811909656551988</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1891403237652041</v>
+        <v>0.301534665236241</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.029852587617409</v>
+        <v>4.097289192500032</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.288075542895954</v>
+        <v>-5.284846025466563</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.801752929638869</v>
+        <v>1.803044736610625</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1891403237652041</v>
+        <v>0.301534665236241</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.03082376537012</v>
+        <v>4.098260370252742</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.237037166889434</v>
+        <v>-5.233807649460043</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.823011184421232</v>
+        <v>1.824302991392988</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1891403237652041</v>
+        <v>0.301534665236241</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.031666669749875</v>
+        <v>4.099103274632498</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.195897872022803</v>
+        <v>-5.192668354593412</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.858505001242029</v>
+        <v>1.859796808213786</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2302796186318349</v>
+        <v>0.3426739601028718</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.075388345543999</v>
+        <v>4.142824950426621</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.085291731943201</v>
+        <v>-5.08206221451381</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.718931453397805</v>
+        <v>1.720223260369561</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3408857587114369</v>
+        <v>0.4532801001824738</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.957936025715695</v>
+        <v>4.025372630598317</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.215872466474043</v>
+        <v>-5.212642949044652</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.670201203659432</v>
+        <v>1.671493010631188</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2103050241805944</v>
+        <v>0.3226993656516313</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.883089629071153</v>
+        <v>3.950526233953775</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.051376132283082</v>
+        <v>-5.048146614853691</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.720426556411899</v>
+        <v>1.721718363383655</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2103050241805944</v>
+        <v>0.3226993656516313</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.867516448147235</v>
+        <v>3.934953053029858</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.078746064967514</v>
+        <v>-5.075516547538123</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.708666293774555</v>
+        <v>1.709958100746312</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2103050241805944</v>
+        <v>0.3226993656516313</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.866704158583665</v>
+        <v>3.934140763466288</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.089131259857403</v>
+        <v>-5.085901742428012</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.714380994943672</v>
+        <v>1.715672801915429</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1999198292907051</v>
+        <v>0.3123141707617419</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.870341820774804</v>
+        <v>3.937778425657426</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.107719418579628</v>
+        <v>-5.104489901150237</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.777782737231207</v>
+        <v>1.779074544202964</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1813316705684797</v>
+        <v>0.2937260120395166</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.930025931317894</v>
+        <v>3.997462536200517</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.108017965275664</v>
+        <v>-5.104788447846273</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.774532329371092</v>
+        <v>1.775824136342848</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1813316705684797</v>
+        <v>0.2937260120395166</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.926894942136192</v>
+        <v>3.994331547018815</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.007194831585236</v>
+        <v>-5.003965314155845</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.819392477786654</v>
+        <v>1.82068428475841</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1937958860528335</v>
+        <v>0.3061902275238704</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.938904366366196</v>
+        <v>4.006340971248818</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.816413470832829</v>
+        <v>-4.813183953403438</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.89583427556616</v>
+        <v>1.897126082537917</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3845772468052409</v>
+        <v>0.4969715882762777</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.053502436296184</v>
+        <v>4.120939041178806</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.797896616791009</v>
+        <v>-4.794667099361618</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.883077862920485</v>
+        <v>1.884369669892241</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.3975073762304491</v>
+        <v>0.509901717701486</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.041097359688905</v>
+        <v>4.108533964571528</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.772703432289691</v>
+        <v>-4.7694739148603</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.92812207333307</v>
+        <v>1.929413880304827</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4227005607317675</v>
+        <v>0.5350949022028043</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.091180207001755</v>
+        <v>4.158616811884377</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.760649305376728</v>
+        <v>-4.757419787947337</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.926630291999693</v>
+        <v>1.927922098971449</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4347546876447303</v>
+        <v>0.5471490291157671</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.09209925105097</v>
+        <v>4.159535855933592</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.767272552067086</v>
+        <v>-4.764043034637695</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.925861623507686</v>
+        <v>1.927153430479442</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4281314409543719</v>
+        <v>0.5405257824254088</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.090005933220891</v>
+        <v>4.157442538103513</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.664391962538494</v>
+        <v>-4.661162445109102</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.979864885197006</v>
+        <v>1.981156692168762</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5310120304829649</v>
+        <v>0.6434063719540017</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.164585312815929</v>
+        <v>4.232021917698551</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.68783400171858</v>
+        <v>-4.684604484289189</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.990690739698565</v>
+        <v>1.991982546670322</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5310120304829649</v>
+        <v>0.6434063719540017</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.184787982989524</v>
+        <v>4.252224587872146</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.705906510010192</v>
+        <v>-4.702676992580801</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.98346173638192</v>
+        <v>1.984753543353677</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5310120304829649</v>
+        <v>0.6434063719540017</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.184787982989524</v>
+        <v>4.252224587872146</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.937080303886824</v>
+        <v>-4.933850786457433</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.851244132424734</v>
+        <v>1.85253593939649</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5310120304829649</v>
+        <v>0.6434063719540017</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.14503989658299</v>
+        <v>4.212476501465613</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.905794283346369</v>
+        <v>-4.902564765916978</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.870781159637856</v>
+        <v>1.872072966609613</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.5622980510234202</v>
+        <v>0.6746923924944571</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.170834127904204</v>
+        <v>4.238270732786826</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.752768891233084</v>
+        <v>-4.749539373803693</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.031162316056074</v>
+        <v>2.03245412302783</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.7153234431367044</v>
+        <v>0.8277177846077413</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.361820362745078</v>
+        <v>4.4292569676277</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.744146567764598</v>
+        <v>3.823349418296177</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.591116686709011</v>
+        <v>-4.756676444988984</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.283289422773996</v>
+        <v>2.217065519462007</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.7153234431367044</v>
+        <v>0.8277177846077413</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.549286587653371</v>
+        <v>4.616723192535993</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240811.xlsx
+++ b/tame_output/ON/bt/strategyON_20240811.xlsx
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>108.9%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>-26.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2052"/>
+  <dimension ref="A1:G2053"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798541</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498868</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705329</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913429</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793907</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982232</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397797</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932772</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917055</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405963</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265648</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284882</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321025</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404856</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636289</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957628</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887749</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.77523303390608</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.823349418296177</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
@@ -48757,6 +48757,29 @@
       </c>
       <c r="G2052" t="n">
         <v>4.616723192535993</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" s="2" t="n">
+        <v>45515</v>
+      </c>
+      <c r="B2053" t="n">
+        <v>3.822480136935856</v>
+      </c>
+      <c r="C2053" t="n">
+        <v>4.205117556102977</v>
+      </c>
+      <c r="D2053" t="n">
+        <v>-4.756676444988984</v>
+      </c>
+      <c r="E2053" t="n">
+        <v>2.217065519462007</v>
+      </c>
+      <c r="F2053" t="n">
+        <v>0.8277177846077413</v>
+      </c>
+      <c r="G2053" t="n">
+        <v>4.198181353089344</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240811.xlsx
+++ b/tame_output/ON/bt/strategyON_20240811.xlsx
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942107</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.773210297111301</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.786949957742306</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316052</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803195</v>
+        <v>3.753571165803197</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809504</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560431</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.721077195472743</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798542</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.68959784049887</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.64306962170533</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729274</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190773</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913431</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532491</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793909</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.75072937701124</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982234</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815461</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131255</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890616</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992196</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489389</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397799</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316254</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105971</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190329</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569622</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557298</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917057</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405965</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.83819962926565</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284884</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321027</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475143</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404858</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882561</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992664</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636291</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.81322282095763</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998759</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896933</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959861</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.79442494194537</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782712</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.78467134563264</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777677</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644416</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799968</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.76667349633112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784112</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155036</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.71289761234307</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389353</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378396</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006979</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585941</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237099</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423391</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973161</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830333</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071555</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868151</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818526</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051791</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679629</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474163</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969546</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700482</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077644</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833462</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077631</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147912</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735281</v>
+        <v>3.834415493735286</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496557</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108861</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.80735616812147</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906083</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912988</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539897</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760318</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781708</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082837</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.730590658677827</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74129851807388</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
@@ -48764,10 +48764,10 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.822480136935856</v>
+        <v>3.822480136935861</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.205117556102977</v>
+        <v>4.205117556102976</v>
       </c>
       <c r="D2053" t="n">
         <v>-4.756676444988984</v>
@@ -48779,7 +48779,7 @@
         <v>0.8277177846077413</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.198181353089344</v>
+        <v>4.198181353089343</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240811.xlsx
+++ b/tame_output/ON/bt/strategyON_20240811.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>110.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-637.2%</t>
+          <t>-635.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-154.5%</t>
+          <t>-153.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-305.6%</t>
+          <t>-440.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-141.2%</t>
+          <t>-150.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-24.3%</t>
         </is>
       </c>
     </row>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798542</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.022502165862416</v>
+        <v>-4.071966581557198</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.186543047201905</v>
+        <v>1.166757280923992</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6785861651513614</v>
+        <v>0.6291217494565808</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.203052036951436</v>
+        <v>3.173373387534567</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.140882838592555</v>
+        <v>-4.190347254287336</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9775464981105026</v>
+        <v>0.9577607318325903</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6113683130003852</v>
+        <v>0.5619038973056046</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.001077045661503</v>
+        <v>2.971398396244635</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.249496917035886</v>
+        <v>-4.298961332730667</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.054250527452376</v>
+        <v>1.034464761174463</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6113683130003852</v>
+        <v>0.5619038973056046</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.121226706380709</v>
+        <v>3.091548056963841</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.214087878787743</v>
+        <v>-4.263552294482524</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.082927168853956</v>
+        <v>1.063141402576044</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6113683130003852</v>
+        <v>0.5619038973056046</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.135739732483032</v>
+        <v>3.106061083066164</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.175704216229592</v>
+        <v>-4.225168631924373</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.095700075219585</v>
+        <v>1.075914308941673</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6497519755585364</v>
+        <v>0.6002875598637558</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.156189371360291</v>
+        <v>3.126510721943423</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.998587886194426</v>
+        <v>-4.048052301889207</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.163275636078954</v>
+        <v>1.143489869801041</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6497519755585364</v>
+        <v>0.6002875598637558</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.152918400205593</v>
+        <v>3.123239750788725</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.043680131027972</v>
+        <v>-4.093144546722753</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.145922129907448</v>
+        <v>1.126136363629536</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5878559323891466</v>
+        <v>0.538391516694366</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.116464166065872</v>
+        <v>3.086785516649004</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.864304709789204</v>
+        <v>-3.913769125483985</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.21145927370937</v>
+        <v>1.191673507431457</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7446326905598653</v>
+        <v>0.6951682748650847</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.204317196274718</v>
+        <v>3.17463854685785</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.90931892330981</v>
+        <v>-3.958783339004591</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.174261043632717</v>
+        <v>1.154475277354805</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7142837952452606</v>
+        <v>0.6648193795504801</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.166915314417545</v>
+        <v>3.137236665000676</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.176323433582246</v>
+        <v>-4.225787849277027</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.073150801862689</v>
+        <v>1.053365035584776</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5199207572023121</v>
+        <v>0.4704563415075315</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.055989053930722</v>
+        <v>3.026310404513853</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.277521215019418</v>
+        <v>-4.3269856307142</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.031875611184321</v>
+        <v>1.012089844906408</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4515119436569929</v>
+        <v>0.4020475279622123</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.014147687700031</v>
+        <v>2.984469038283163</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.271010248405106</v>
+        <v>-4.320474664099887</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.032079959384363</v>
+        <v>1.01229419310645</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4515119436569929</v>
+        <v>0.4020475279622123</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.011747649254348</v>
+        <v>2.98206899983748</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.251972120697808</v>
+        <v>-4.30143653639259</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.036219929675527</v>
+        <v>1.016434163397614</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3933283323257984</v>
+        <v>0.3438639166310178</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.973362201663877</v>
+        <v>2.943683552247008</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.304487922972629</v>
+        <v>-4.35395233866741</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.134508010399789</v>
+        <v>1.114722244121876</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3933283323257984</v>
+        <v>0.3438639166310178</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.092656603298067</v>
+        <v>3.062977953881199</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.38612833436817</v>
+        <v>-4.367819100001328</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.102685174827706</v>
+        <v>1.110008868574443</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3968615895719985</v>
+        <v>0.3060059998971948</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.09560988663192</v>
+        <v>3.041096532827038</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.34132416282824</v>
+        <v>-4.323014928461398</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.126615373840604</v>
+        <v>1.13393906758734</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3968615895719985</v>
+        <v>0.3060059998971948</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.101618417028846</v>
+        <v>3.047105063223964</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.193581192593237</v>
+        <v>-4.175271958226396</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.083662783211804</v>
+        <v>1.090986476958541</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5646689468068817</v>
+        <v>0.473813357132078</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.100253052646976</v>
+        <v>3.045739698842094</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.277402413867936</v>
+        <v>-4.259093179501094</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.052927916233406</v>
+        <v>1.060251609980143</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5646689468068817</v>
+        <v>0.473813357132078</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.103046674178457</v>
+        <v>3.048533320373575</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.271249707815151</v>
+        <v>-4.25294047344831</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.056051347046178</v>
+        <v>1.063375040792915</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.570821652859666</v>
+        <v>0.4799660631848623</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.107400646201786</v>
+        <v>3.052887292396903</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.288059005965653</v>
+        <v>-4.269749771598812</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.048408104526088</v>
+        <v>1.055731798272824</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5540123547091644</v>
+        <v>0.4631567650343607</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.096395544051595</v>
+        <v>3.041882190246713</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.225761007189531</v>
+        <v>-4.207451772822689</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.139662857833357</v>
+        <v>1.146986551580094</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5993066189836065</v>
+        <v>0.5084510293088027</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.189907656413081</v>
+        <v>3.135394302608199</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.023970809524373</v>
+        <v>-4.005661575157531</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.022670938613548</v>
+        <v>1.029994632360284</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7973248111527609</v>
+        <v>0.7064692214779571</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.111010573428701</v>
+        <v>3.056497219623818</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.074857522210568</v>
+        <v>-4.056548287843726</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.072606485861245</v>
+        <v>1.079930179607982</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7464380984665664</v>
+        <v>0.6555825087917626</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.15076877813916</v>
+        <v>3.096255424334277</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.988246779560761</v>
+        <v>-3.969937545193919</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.121878519037211</v>
+        <v>1.129202212783948</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8250638296717246</v>
+        <v>0.7342082399969209</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.212571952978298</v>
+        <v>3.158058599173416</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.048456077566045</v>
+        <v>-4.030146843199203</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.096330780659769</v>
+        <v>1.103654474406506</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7648545316664401</v>
+        <v>0.6739989419916363</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.174982354999799</v>
+        <v>3.120469001194917</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.972034031134118</v>
+        <v>-3.953724796767276</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.125391217272468</v>
+        <v>1.132714911019205</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7648545316664401</v>
+        <v>0.6739989419916363</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.173473973039727</v>
+        <v>3.118960619234845</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.92766089949555</v>
+        <v>-3.909351665128708</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.143003337363332</v>
+        <v>1.150327031110069</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8092276633050087</v>
+        <v>0.7183720736302049</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.199960719458305</v>
+        <v>3.145447365653423</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.950141250354434</v>
+        <v>-3.931832015987593</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.128404991158369</v>
+        <v>1.135728684905106</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8092276633050087</v>
+        <v>0.7183720736302049</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.194354513596895</v>
+        <v>3.139841159792013</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.902485519793379</v>
+        <v>-3.884176285426537</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.153849040410596</v>
+        <v>1.161172734157333</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8568833938660644</v>
+        <v>0.7660278041912606</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.229329708961333</v>
+        <v>3.174816355156451</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.801967361294624</v>
+        <v>-3.783658126927782</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.198948677184823</v>
+        <v>1.206272370931559</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9574015523648189</v>
+        <v>0.8665459626900152</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.294532977435311</v>
+        <v>3.240019623630428</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.786062031862271</v>
+        <v>-3.767752797495429</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.192065481433636</v>
+        <v>1.199389175180372</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.87828889165558</v>
+        <v>0.7874333019807762</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.23382005348564</v>
+        <v>3.179306699680757</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.741223630253873</v>
+        <v>-3.722914395887031</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.214098544687624</v>
+        <v>1.22142223843436</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8828323246004495</v>
+        <v>0.7919767349256457</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.24064381586319</v>
+        <v>3.186130462058308</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.760722086495881</v>
+        <v>-3.74241285212904</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.210460101821898</v>
+        <v>1.217783795568635</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8347476833205452</v>
+        <v>0.7438920936457414</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.215953970726325</v>
+        <v>3.161440616921443</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.716519249409981</v>
+        <v>-3.698210015043139</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.234020839184096</v>
+        <v>1.241344532930832</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8789505204064456</v>
+        <v>0.7880949307316418</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.248355275505703</v>
+        <v>3.19384192170082</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.753498277073424</v>
+        <v>-3.735189042706582</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.217639228587966</v>
+        <v>1.224962922334702</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9159244221977761</v>
+        <v>0.8250688325229724</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.268949617049749</v>
+        <v>3.214436263244866</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.595206859534152</v>
+        <v>-3.57689762516731</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.332203560786714</v>
+        <v>1.339527254533451</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9159244221977761</v>
+        <v>0.8250688325229724</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.320197382232788</v>
+        <v>3.265684028427906</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.387564855899676</v>
+        <v>-3.369255621532834</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.413701066834758</v>
+        <v>1.421024760581495</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.123566425832252</v>
+        <v>1.032710836157448</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.443223289007727</v>
+        <v>3.388709935202845</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.336532763177148</v>
+        <v>-3.318223528810306</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.429062132162039</v>
+        <v>1.436385825908776</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.17459851855478</v>
+        <v>1.083742928879976</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.468790772879514</v>
+        <v>3.414277419074632</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.271308582049942</v>
+        <v>-3.2529993476831</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.472339208705626</v>
+        <v>1.479662902452363</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.239822699681986</v>
+        <v>1.148967110007182</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.525112685648542</v>
+        <v>3.47059933184366</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.233881561978808</v>
+        <v>-3.215572327611966</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.48327098903336</v>
+        <v>1.490594682780097</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.245074237711168</v>
+        <v>1.154218648036364</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.524224580765332</v>
+        <v>3.469711226960449</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.253993218013516</v>
+        <v>-3.235683983646675</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.476483118950717</v>
+        <v>1.483806812697454</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.256101582708587</v>
+        <v>1.165245993033783</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.532097780095024</v>
+        <v>3.477584426290141</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.200248403586312</v>
+        <v>-3.18193916921947</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.65853881574281</v>
+        <v>1.665862509489547</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.266164892149049</v>
+        <v>1.175309302474245</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.698693536780512</v>
+        <v>3.644180182975629</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.125466142561299</v>
+        <v>-3.107156908194457</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.808564629370632</v>
+        <v>1.815888323117369</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.340947153174062</v>
+        <v>1.250091563499258</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.863675802613336</v>
+        <v>3.809162448808454</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.099382058297491</v>
+        <v>-3.081072823930649</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.810706239090014</v>
+        <v>1.818029932836751</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.340947153174062</v>
+        <v>1.250091563499258</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.855383778627195</v>
+        <v>3.800870424822313</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.011504145188371</v>
+        <v>-2.993194910821529</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.844050599917442</v>
+        <v>1.851374293664179</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.456872795597413</v>
+        <v>1.366017205922609</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.923132359664986</v>
+        <v>3.868619005860103</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.002611683795087</v>
+        <v>-2.984302449428245</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.865161990201547</v>
+        <v>1.872485683948284</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.456872795597413</v>
+        <v>1.366017205922609</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.940686765391777</v>
+        <v>3.886173411586895</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.79442494194537</v>
+        <v>3.794424941945369</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.171087800764965</v>
+        <v>-3.152778566398123</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.78962659081818</v>
+        <v>1.796950284564916</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.428924959880832</v>
+        <v>1.338069370206028</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.915773111366413</v>
+        <v>3.86125975756153</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782712</v>
+        <v>3.795574066782711</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.473288271903382</v>
+        <v>-2.45497903753654</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.050016099550675</v>
+        <v>2.057339793297412</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.358576900510422</v>
+        <v>1.267721310835618</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.854833972932028</v>
+        <v>3.800320619127146</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563264</v>
+        <v>3.784671345632639</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.450567168220229</v>
+        <v>-2.432257933853387</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.04976856352084</v>
+        <v>2.057092257267577</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.358576900510422</v>
+        <v>1.267721310835618</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.845497995428933</v>
+        <v>3.79098464162405</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777677</v>
+        <v>3.783205696777676</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.579768981514272</v>
+        <v>-2.56145974714743</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.156993964054393</v>
+        <v>2.164317657801129</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.229375087216379</v>
+        <v>1.138519497541575</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.926883033303676</v>
+        <v>3.872369679498794</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644416</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.734549988292527</v>
+        <v>-2.716240753925685</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.132159383836737</v>
+        <v>2.139483077583473</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.196007413161903</v>
+        <v>1.105151823487099</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.943940251364637</v>
+        <v>3.889426897559755</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799968</v>
+        <v>3.769443619799967</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.727495298077354</v>
+        <v>-2.709186063710512</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.131656615912351</v>
+        <v>2.138980309659088</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.203062103377077</v>
+        <v>1.112206513702273</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.944848421483287</v>
+        <v>3.890335067678404</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633112</v>
+        <v>3.766673496331119</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.700544073750866</v>
+        <v>-2.682234839384024</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.152443259287688</v>
+        <v>2.159766953034425</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.217942449404796</v>
+        <v>1.127086859729992</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.963782782744659</v>
+        <v>3.909269428939777</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784112</v>
+        <v>3.768052067784111</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.836497081807182</v>
+        <v>-2.81818784744034</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.282165188210121</v>
+        <v>2.289488881956858</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.217942449404796</v>
+        <v>1.127086859729992</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.14788591488962</v>
+        <v>4.093372561084736</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.858905199612054</v>
+        <v>-2.840595965245212</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.265318635991166</v>
+        <v>2.272642329737902</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.217942449404796</v>
+        <v>1.127086859729992</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.140002609792613</v>
+        <v>4.08548925598773</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155036</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.887129435189654</v>
+        <v>-2.868820200822813</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.256082941309763</v>
+        <v>2.2634066350565</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.235919201856105</v>
+        <v>1.145063612181301</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.152842660813035</v>
+        <v>4.098329307008153</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.896570361078184</v>
+        <v>-2.878261126711342</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.308560288676198</v>
+        <v>2.315883982422935</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.358346319399496</v>
+        <v>1.267490729724692</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.282552649060917</v>
+        <v>4.228039295256035</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321638</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.948843968413826</v>
+        <v>-2.930534734046984</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.290541940287242</v>
+        <v>2.297865634033979</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.306072712063855</v>
+        <v>1.215217122389051</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.254079579204833</v>
+        <v>4.199566225399951</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347707</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.025173946014732</v>
+        <v>-3.00686471164789</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.258121762140656</v>
+        <v>2.265445455887392</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.306072712063855</v>
+        <v>1.215217122389051</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.252191392098609</v>
+        <v>4.197678038293726</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887751</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.227427666339085</v>
+        <v>-3.209118431972243</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.172040503613776</v>
+        <v>2.179364197360513</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.103818991739501</v>
+        <v>1.012963402064697</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.125659389506859</v>
+        <v>4.071146035701976</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.71289761234307</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.38899609186634</v>
+        <v>-3.370686857499498</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.105847143613027</v>
+        <v>2.113170837359763</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.977036067941622</v>
+        <v>0.886180478266818</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.048023645438283</v>
+        <v>3.993510291633401</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389353</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.521297383963893</v>
+        <v>-3.502988149597051</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.066000033639924</v>
+        <v>2.07332372738666</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.977036067941622</v>
+        <v>0.886180478266818</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.061097052304202</v>
+        <v>4.00658369849932</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378396</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.707165694803123</v>
+        <v>-3.688856460436281</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.983657906087172</v>
+        <v>1.990981599833908</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8184704746216743</v>
+        <v>0.7276148849468703</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.957962893095173</v>
+        <v>3.903449539290291</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006979</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.735066481912596</v>
+        <v>-3.716757247545754</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.971021632370385</v>
+        <v>1.978345326117121</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7838735504787395</v>
+        <v>0.6930179608039355</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.935728779736414</v>
+        <v>3.881215425931532</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.85759258461549</v>
+        <v>-3.839283350248648</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.918775635266426</v>
+        <v>1.926099329013162</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6613474477758456</v>
+        <v>0.5704918581010416</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.858977562091877</v>
+        <v>3.804464208286994</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585941</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.088107080801079</v>
+        <v>-4.069797846434237</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.893275796382694</v>
+        <v>1.900599490129431</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4308329515902569</v>
+        <v>0.3399773619154529</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.787374823971027</v>
+        <v>3.732861470166145</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814668</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.344827898795902</v>
+        <v>-4.326518664429061</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.930899188186612</v>
+        <v>1.938222881933348</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3224183774464421</v>
+        <v>0.2315627877716381</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.862637798486586</v>
+        <v>3.808124444681703</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237099</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.498814316572043</v>
+        <v>-4.480505082205202</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.938284890221795</v>
+        <v>1.945608583968532</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3224183774464421</v>
+        <v>0.2315627877716381</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.931618067632225</v>
+        <v>3.877104713827343</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423391</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.448292412744377</v>
+        <v>-4.429983178377536</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.944544853872983</v>
+        <v>1.951868547619719</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3224183774464421</v>
+        <v>0.2315627877716381</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.917669269752346</v>
+        <v>3.863155915947464</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.700767566752101</v>
+        <v>-4.68245833238526</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.855425281325307</v>
+        <v>1.862748975072043</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3224183774464421</v>
+        <v>0.2315627877716381</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.92953975880776</v>
+        <v>3.875026405002878</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973161</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.993663323231513</v>
+        <v>-4.975354088864672</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.739477513252486</v>
+        <v>1.746801206999222</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3224183774464421</v>
+        <v>0.2315627877716381</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.930750293326704</v>
+        <v>3.876236939521821</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.151207394960955</v>
+        <v>-5.132898160594114</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.68058162678803</v>
+        <v>1.687905320534767</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2555165723061676</v>
+        <v>0.1646609826313636</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.89473095246986</v>
+        <v>3.840217598664978</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916205</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.429171790544228</v>
+        <v>-5.410862556177388</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.564473721290911</v>
+        <v>1.571797415037647</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1658968380206833</v>
+        <v>0.07504124834587933</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.83603696463476</v>
+        <v>3.781523610829877</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830333</v>
+        <v>3.667962306830331</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.546139483183119</v>
+        <v>-5.527830248816278</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.679890700934398</v>
+        <v>1.687214394681134</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1658968380206833</v>
+        <v>0.07504124834587933</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.998241021333803</v>
+        <v>3.943727667528921</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071555</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.630857425404073</v>
+        <v>-5.612548191037232</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.640850162009831</v>
+        <v>1.648173855756567</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.08078080909263696</v>
+        <v>-0.01007478058216704</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.94201804194079</v>
+        <v>3.887504688135907</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868151</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.712792243672956</v>
+        <v>-5.694483009306115</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.618305652270769</v>
+        <v>1.625629346017505</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.07084606350555678</v>
+        <v>-0.02000952616924723</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.946286612157033</v>
+        <v>3.89177325835215</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.814768365921363</v>
+        <v>-5.796459131554522</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.586440841827308</v>
+        <v>1.593764535574045</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.0311300587428508</v>
+        <v>-0.1219856484176548</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.894026577263891</v>
+        <v>3.839513223459008</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.704762082444142</v>
+        <v>-5.686452848077301</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.622596242462373</v>
+        <v>1.629919936209109</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.007925486825575589</v>
+        <v>-0.09878107650037959</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.900102207658431</v>
+        <v>3.845588853853549</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818526</v>
+        <v>3.785563924818524</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.561702506703217</v>
+        <v>-5.543393272336376</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.684070083480717</v>
+        <v>1.691393777227453</v>
       </c>
       <c r="F2028" t="n">
-        <v>8.793976440368834e-05</v>
+        <v>-0.09076764991040032</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.909160274334393</v>
+        <v>3.854646920529511</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051791</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.260255781231379</v>
+        <v>-5.241946546864538</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.811909656551988</v>
+        <v>1.819233350298724</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.301534665236241</v>
+        <v>0.2106790755614369</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.097289192500032</v>
+        <v>4.04277583869515</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679629</v>
+        <v>3.812635940679627</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.284846025466563</v>
+        <v>-5.266536791099722</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.803044736610625</v>
+        <v>1.810368430357361</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.301534665236241</v>
+        <v>0.2106790755614369</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.098260370252742</v>
+        <v>4.04374701644786</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474163</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.233807649460043</v>
+        <v>-5.215498415093202</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.824302991392988</v>
+        <v>1.831626685139724</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.301534665236241</v>
+        <v>0.2106790755614369</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.099103274632498</v>
+        <v>4.044589920827615</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969546</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.192668354593412</v>
+        <v>-5.174359120226571</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.859796808213786</v>
+        <v>1.867120501960522</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3426739601028718</v>
+        <v>0.2518183704280678</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.142824950426621</v>
+        <v>4.088311596621739</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700482</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.08206221451381</v>
+        <v>-5.063752980146969</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.720223260369561</v>
+        <v>1.727546954116297</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4532801001824738</v>
+        <v>0.3624245105076698</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.025372630598317</v>
+        <v>3.970859276793434</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077644</v>
+        <v>3.804688961077642</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.212642949044652</v>
+        <v>-5.194333714677811</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.671493010631188</v>
+        <v>1.678816704377924</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3226993656516313</v>
+        <v>0.2318437759768273</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.950526233953775</v>
+        <v>3.896012880148893</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.048146614853691</v>
+        <v>-5.02983738048685</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.721718363383655</v>
+        <v>1.729042057130391</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3226993656516313</v>
+        <v>0.2318437759768273</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.934953053029858</v>
+        <v>3.880439699224975</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077631</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.075516547538123</v>
+        <v>-5.057207313171282</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.709958100746312</v>
+        <v>1.717281794493049</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3226993656516313</v>
+        <v>0.2318437759768273</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.934140763466288</v>
+        <v>3.879627409661405</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147912</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.085901742428012</v>
+        <v>-5.067592508061171</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.715672801915429</v>
+        <v>1.722996495662165</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3123141707617419</v>
+        <v>0.2214585810869379</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.937778425657426</v>
+        <v>3.883265071852544</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735286</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.104489901150237</v>
+        <v>-5.086180666783396</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.779074544202964</v>
+        <v>1.7863982379497</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2937260120395166</v>
+        <v>0.2028704223647126</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.997462536200517</v>
+        <v>3.942949182395633</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496557</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.104788447846273</v>
+        <v>-5.086479213479432</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.775824136342848</v>
+        <v>1.783147830089584</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2937260120395166</v>
+        <v>0.2028704223647126</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.994331547018815</v>
+        <v>3.939818193213933</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108861</v>
+        <v>3.815643212108859</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.003965314155845</v>
+        <v>-4.985656079789004</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.82068428475841</v>
+        <v>1.828007978505147</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3061902275238704</v>
+        <v>0.2153346378490664</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.006340971248818</v>
+        <v>3.951827617443936</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812147</v>
+        <v>3.807356168121468</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.813183953403438</v>
+        <v>-4.794874719036597</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.897126082537917</v>
+        <v>1.904449776284653</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4969715882762777</v>
+        <v>0.4061159986014738</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.120939041178806</v>
+        <v>4.066425687373924</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906083</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.794667099361618</v>
+        <v>-4.776357864994777</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.884369669892241</v>
+        <v>1.891693363638978</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.509901717701486</v>
+        <v>0.419046128026682</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.108533964571528</v>
+        <v>4.054020610766645</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912988</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.7694739148603</v>
+        <v>-4.751164680493459</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.929413880304827</v>
+        <v>1.936737574051563</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5350949022028043</v>
+        <v>0.4442393125280004</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.158616811884377</v>
+        <v>4.104103458079495</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539897</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.757419787947337</v>
+        <v>-4.739110553580496</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.927922098971449</v>
+        <v>1.935245792718186</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5471490291157671</v>
+        <v>0.4562934394409632</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.159535855933592</v>
+        <v>4.10502250212871</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.764043034637695</v>
+        <v>-4.745733800270854</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.927153430479442</v>
+        <v>1.934477124226179</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5405257824254088</v>
+        <v>0.4496701927506048</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.157442538103513</v>
+        <v>4.102929184298631</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.661162445109102</v>
+        <v>-4.642853210742262</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.981156692168762</v>
+        <v>1.988480385915498</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6434063719540017</v>
+        <v>0.5525507822791977</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.232021917698551</v>
+        <v>4.177508563893669</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760318</v>
+        <v>3.646857607760316</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.684604484289189</v>
+        <v>-4.666295249922348</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.991982546670322</v>
+        <v>1.999306240417058</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6434063719540017</v>
+        <v>0.5525507822791977</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.252224587872146</v>
+        <v>4.197711234067263</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781708</v>
+        <v>3.666767386781706</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.702676992580801</v>
+        <v>-4.68436775821396</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.984753543353677</v>
+        <v>1.992077237100413</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6434063719540017</v>
+        <v>0.5525507822791977</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.252224587872146</v>
+        <v>4.197711234067263</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082837</v>
+        <v>3.670068888082835</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.933850786457433</v>
+        <v>-4.915541552090592</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.85253593939649</v>
+        <v>1.859859633143227</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6434063719540017</v>
+        <v>0.5525507822791977</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.212476501465613</v>
+        <v>4.157963147660729</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943589</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.902564765916978</v>
+        <v>-4.884255531550137</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.872072966609613</v>
+        <v>1.879396660356349</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6746923924944571</v>
+        <v>0.5838368028196531</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.238270732786826</v>
+        <v>4.183757378981943</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677827</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.749539373803693</v>
+        <v>-4.731230139436852</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.03245412302783</v>
+        <v>2.039777816774567</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8277177846077413</v>
+        <v>0.7368621949329373</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.4292569676277</v>
+        <v>4.374743613822818</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073886</v>
+        <v>3.741298518073884</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.756676444988984</v>
+        <v>-4.738367210622143</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.217065519462007</v>
+        <v>2.224389213208743</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8277177846077413</v>
+        <v>0.7368621949329373</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.616723192535993</v>
+        <v>4.562209838731111</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.822480136935861</v>
+        <v>3.822546110568343</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.205117556102976</v>
+        <v>4.22426874529137</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.756676444988984</v>
+        <v>-4.738367210622143</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.217065519462007</v>
+        <v>2.224389213208743</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8277177846077413</v>
+        <v>0.7368621949329373</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.198181353089343</v>
+        <v>4.217332542277738</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240811.xlsx
+++ b/tame_output/ON/bt/strategyON_20240811.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>87.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.7%</t>
+          <t>428.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-635.4%</t>
+          <t>-646.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-153.8%</t>
+          <t>-158.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-440.8%</t>
+          <t>-269.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.3%</t>
+          <t>-145.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-47.9%</t>
         </is>
       </c>
     </row>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.369696245220947</v>
+        <v>-5.532205174899443</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8085685156852387</v>
+        <v>0.7435649438138405</v>
       </c>
       <c r="F1919" t="n">
         <v>0.1360058417680366</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.193804152753515</v>
+        <v>-5.35631308243201</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8825244761928603</v>
+        <v>0.8175209043214626</v>
       </c>
       <c r="F1920" t="n">
         <v>0.1360058417680366</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.022357689731051</v>
+        <v>-5.184866619409546</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9644305674563993</v>
+        <v>0.8994269955850016</v>
       </c>
       <c r="F1921" t="n">
         <v>0.3074523047904997</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.948068123992712</v>
+        <v>-5.110577053671207</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9931668713680322</v>
+        <v>0.9281632994966342</v>
       </c>
       <c r="F1922" t="n">
         <v>0.381741870528839</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.884432381758778</v>
+        <v>-5.046941311437273</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.023315969315923</v>
+        <v>0.9583123974445251</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4453776127627735</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.773005622432858</v>
+        <v>-4.935514552111353</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.049080931830087</v>
+        <v>0.9840773599586889</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4453776127627735</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.783508245498147</v>
+        <v>-4.946017175176642</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.046622959228849</v>
+        <v>0.9816193873574508</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4348749896974847</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.711265677326952</v>
+        <v>-4.873774607005447</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.079449300332147</v>
+        <v>1.014445728460749</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4348749896974847</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.693551990449087</v>
+        <v>-4.856060920127582</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.087213359000633</v>
+        <v>1.022209787129235</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4380563185944015</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.58474710496936</v>
+        <v>-4.747256034647855</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.127733384412517</v>
+        <v>1.062729812541119</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4380563185944015</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.364726306932349</v>
+        <v>-4.527235236610844</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.217320740637936</v>
+        <v>1.152317168766538</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5792761636623818</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.231858617869071</v>
+        <v>-4.394367547547566</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.28636199906507</v>
+        <v>1.221358427193672</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5792761636623818</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.111685534504573</v>
+        <v>-4.274194464183068</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.335577076851171</v>
+        <v>1.270573504979773</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6994492470268807</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577001</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.976432173174596</v>
+        <v>-4.13894110285309</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.399766523944602</v>
+        <v>1.334762952073204</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8347026083568578</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942107</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.036307000532288</v>
+        <v>-4.198815930210783</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.361854084402951</v>
+        <v>1.296850512531553</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7748277809991657</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.91648676962145</v>
+        <v>-4.078995699299946</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.425071346001494</v>
+        <v>1.360067774130096</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7748277809991657</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.918956476083256</v>
+        <v>-4.081465405761752</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.331727662739214</v>
+        <v>1.266724090867815</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7723580745373595</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.987326662407266</v>
+        <v>-4.149835592085762</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.223641449694911</v>
+        <v>1.158637877823513</v>
       </c>
       <c r="F1936" t="n">
         <v>0.7816337735735744</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.001114715254313</v>
+        <v>-4.163623644932809</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.208562937187984</v>
+        <v>1.143559365316585</v>
       </c>
       <c r="F1937" t="n">
         <v>0.7816337735735744</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.056634791146903</v>
+        <v>-4.219143720825398</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.32338574352315</v>
+        <v>1.258382171651752</v>
       </c>
       <c r="F1938" t="n">
         <v>0.7816337735735744</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.881160531354433</v>
+        <v>-4.043669461032929</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.398142679431926</v>
+        <v>1.333139107560527</v>
       </c>
       <c r="F1939" t="n">
         <v>0.7816337735735744</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225448</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.992096783995682</v>
+        <v>-4.154605713674178</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.329510207136633</v>
+        <v>1.264506635265235</v>
       </c>
       <c r="F1940" t="n">
         <v>0.7816337735735744</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111301</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.9584332385234</v>
+        <v>-4.120942168201895</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.271513938726996</v>
+        <v>1.206510366855598</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8152973190458563</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.898580619319677</v>
+        <v>-4.061089548998172</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.305627372840617</v>
+        <v>1.240623800969219</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8152973190458563</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742306</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.8123371562933</v>
+        <v>-3.974846085971794</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.335071028625029</v>
+        <v>1.270067456753631</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8152973190458563</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316052</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.857643975692279</v>
+        <v>-4.020152905370774</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.308724076309962</v>
+        <v>1.243720504438564</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7744871560366255</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803197</v>
+        <v>3.753571165803195</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.886677080394581</v>
+        <v>-4.049186010073075</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.297662707462143</v>
+        <v>1.232659135590745</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7744871560366255</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809504</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.793866598943722</v>
+        <v>-3.956375528622216</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.264059591933853</v>
+        <v>1.199056020062455</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8672976374874849</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560431</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.838256068273149</v>
+        <v>-4.000764997951643</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.248177280126682</v>
+        <v>1.183173708255285</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8229081681580572</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472743</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.954797673378492</v>
+        <v>-4.117306603056987</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.196636346596268</v>
+        <v>1.13163277472487</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7063665630527145</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.994721767961064</v>
+        <v>-4.157230697639559</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.186158004593907</v>
+        <v>1.121154432722509</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7063665630527145</v>
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049887</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.071966581557198</v>
+        <v>-4.185011095540911</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.166757280923992</v>
+        <v>1.121539475330507</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6291217494565808</v>
+        <v>0.6785861651513614</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.173373387534567</v>
+        <v>3.203052036951436</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170533</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.190347254287336</v>
+        <v>-4.30339176827105</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9577607318325903</v>
+        <v>0.9125429262391047</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5619038973056046</v>
+        <v>0.6113683130003852</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.971398396244635</v>
+        <v>3.001077045661503</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729274</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.298961332730667</v>
+        <v>-4.412005846714381</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.034464761174463</v>
+        <v>0.989246955580978</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5619038973056046</v>
+        <v>0.6113683130003852</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.091548056963841</v>
+        <v>3.121226706380709</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190773</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.263552294482524</v>
+        <v>-4.376596808466238</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.063141402576044</v>
+        <v>1.017923596982558</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5619038973056046</v>
+        <v>0.6113683130003852</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.106061083066164</v>
+        <v>3.135739732483032</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913431</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.225168631924373</v>
+        <v>-4.338213145908087</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.075914308941673</v>
+        <v>1.030696503348187</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6002875598637558</v>
+        <v>0.6497519755585364</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.126510721943423</v>
+        <v>3.156189371360291</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532491</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.048052301889207</v>
+        <v>-4.161096815872921</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.143489869801041</v>
+        <v>1.098272064207555</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6002875598637558</v>
+        <v>0.6497519755585364</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.123239750788725</v>
+        <v>3.152918400205593</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793909</v>
+        <v>3.741328448793907</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.093144546722753</v>
+        <v>-4.206189060706467</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.126136363629536</v>
+        <v>1.08091855803605</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.538391516694366</v>
+        <v>0.5878559323891466</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.086785516649004</v>
+        <v>3.116464166065872</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072937701124</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.913769125483985</v>
+        <v>-4.026813639467699</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.191673507431457</v>
+        <v>1.146455701837972</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6951682748650847</v>
+        <v>0.7446326905598653</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.17463854685785</v>
+        <v>3.204317196274718</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982234</v>
+        <v>3.716991718982232</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.958783339004591</v>
+        <v>-4.071827852988305</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.154475277354805</v>
+        <v>1.109257471761319</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6648193795504801</v>
+        <v>0.7142837952452606</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.137236665000676</v>
+        <v>3.166915314417545</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.225787849277027</v>
+        <v>-4.33883236326074</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.053365035584776</v>
+        <v>1.008147229991291</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4704563415075315</v>
+        <v>0.5199207572023121</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.026310404513853</v>
+        <v>3.055989053930722</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760817</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.3269856307142</v>
+        <v>-4.440030144697912</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.012089844906408</v>
+        <v>0.9668720393129233</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4020475279622123</v>
+        <v>0.4515119436569929</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.984469038283163</v>
+        <v>3.014147687700031</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815461</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.320474664099887</v>
+        <v>-4.4335191780836</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.01229419310645</v>
+        <v>0.9670763875129651</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4020475279622123</v>
+        <v>0.4515119436569929</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.98206899983748</v>
+        <v>3.011747649254348</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378106</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.30143653639259</v>
+        <v>-4.414481050376303</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.016434163397614</v>
+        <v>0.9712163578041288</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3438639166310178</v>
+        <v>0.3933283323257984</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.943683552247008</v>
+        <v>2.973362201663877</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131255</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.35395233866741</v>
+        <v>-4.466996852651123</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.114722244121876</v>
+        <v>1.069504438528391</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3438639166310178</v>
+        <v>0.3933283323257984</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.062977953881199</v>
+        <v>3.092656603298067</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.367819100001328</v>
+        <v>-4.480863613985041</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.110008868574443</v>
+        <v>1.064791062980957</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3060059998971948</v>
+        <v>0.3554704155919755</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.041096532827038</v>
+        <v>3.070775182243906</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789126</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.323014928461398</v>
+        <v>-4.436059442445111</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.13393906758734</v>
+        <v>1.088721261993855</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3060059998971948</v>
+        <v>0.3554704155919755</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.047105063223964</v>
+        <v>3.076783712640832</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519913</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.175271958226396</v>
+        <v>-4.288316472210108</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.090986476958541</v>
+        <v>1.045768671365056</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.473813357132078</v>
+        <v>0.5232777728268586</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.045739698842094</v>
+        <v>3.075418348258962</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.259093179501094</v>
+        <v>-4.372137693484807</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.060251609980143</v>
+        <v>1.015033804386658</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.473813357132078</v>
+        <v>0.5232777728268586</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.048533320373575</v>
+        <v>3.078211969790443</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.25294047344831</v>
+        <v>-4.365984987432022</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.063375040792915</v>
+        <v>1.01815723519943</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4799660631848623</v>
+        <v>0.5294304788796429</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.052887292396903</v>
+        <v>3.082565941813772</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890616</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.269749771598812</v>
+        <v>-4.382794285582524</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.055731798272824</v>
+        <v>1.010513992679339</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4631567650343607</v>
+        <v>0.5126211807291412</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.041882190246713</v>
+        <v>3.071560839663581</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798431</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.207451772822689</v>
+        <v>-4.320496286806402</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.146986551580094</v>
+        <v>1.101768745986609</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5084510293088027</v>
+        <v>0.5579154450035833</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.135394302608199</v>
+        <v>3.165072952025067</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992196</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.005661575157531</v>
+        <v>-4.118706089141244</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.029994632360284</v>
+        <v>0.9847768267667991</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7064692214779571</v>
+        <v>0.7559336371727376</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.056497219623818</v>
+        <v>3.086175869040687</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.056548287843726</v>
+        <v>-4.169592801827439</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.079930179607982</v>
+        <v>1.034712374014497</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6555825087917626</v>
+        <v>0.7050469244865432</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.096255424334277</v>
+        <v>3.125934073751146</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.969937545193919</v>
+        <v>-4.082982059177632</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.129202212783948</v>
+        <v>1.083984407190463</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7342082399969209</v>
+        <v>0.7836726556917014</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.158058599173416</v>
+        <v>3.187737248590284</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489389</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.030146843199203</v>
+        <v>-4.143191357182917</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.103654474406506</v>
+        <v>1.05843666881302</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6739989419916363</v>
+        <v>0.7234633576864169</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.120469001194917</v>
+        <v>3.150147650611785</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397799</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.953724796767276</v>
+        <v>-4.06676931075099</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.132714911019205</v>
+        <v>1.08749710542572</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6739989419916363</v>
+        <v>0.7234633576864169</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.118960619234845</v>
+        <v>3.148639268651714</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316254</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.909351665128708</v>
+        <v>-4.022396179112421</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.150327031110069</v>
+        <v>1.105109225516584</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7183720736302049</v>
+        <v>0.7678364893249855</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.145447365653423</v>
+        <v>3.175126015070291</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105971</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.931832015987593</v>
+        <v>-4.044876529971306</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.135728684905106</v>
+        <v>1.09051087931162</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7183720736302049</v>
+        <v>0.7678364893249855</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.139841159792013</v>
+        <v>3.169519809208881</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190329</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.884176285426537</v>
+        <v>-3.99722079941025</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.161172734157333</v>
+        <v>1.115954928563847</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7660278041912606</v>
+        <v>0.8154922198860411</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.174816355156451</v>
+        <v>3.20449500457332</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569622</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.783658126927782</v>
+        <v>-3.896702640911496</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.206272370931559</v>
+        <v>1.161054565338074</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8665459626900152</v>
+        <v>0.9160103783847957</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.240019623630428</v>
+        <v>3.269698273047297</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557298</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.767752797495429</v>
+        <v>-3.880797311479143</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.199389175180372</v>
+        <v>1.154171369586887</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7874333019807762</v>
+        <v>0.8368977176755568</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.179306699680757</v>
+        <v>3.208985349097626</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932774</v>
+        <v>3.816837033932772</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.722914395887031</v>
+        <v>-3.835958909870745</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.22142223843436</v>
+        <v>1.176204432840875</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7919767349256457</v>
+        <v>0.8414411506204262</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.186130462058308</v>
+        <v>3.215809111475176</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917057</v>
+        <v>3.817932354917055</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.74241285212904</v>
+        <v>-3.855457366112753</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.217783795568635</v>
+        <v>1.172565989975149</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7438920936457414</v>
+        <v>0.7933565093405219</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.161440616921443</v>
+        <v>3.191119266338311</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405965</v>
+        <v>3.826684745405962</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.698210015043139</v>
+        <v>-3.811254529026853</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.241344532930832</v>
+        <v>1.196126727337347</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7880949307316418</v>
+        <v>0.8375593464264224</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.19384192170082</v>
+        <v>3.223520571117689</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926565</v>
+        <v>3.838199629265647</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.735189042706582</v>
+        <v>-3.848233556690296</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.224962922334702</v>
+        <v>1.179745116741217</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8250688325229724</v>
+        <v>0.8745332482177529</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.214436263244866</v>
+        <v>3.244114912661735</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284884</v>
+        <v>3.863895080284882</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.57689762516731</v>
+        <v>-3.689942139151024</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.339527254533451</v>
+        <v>1.294309448939966</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8250688325229724</v>
+        <v>0.8745332482177529</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.265684028427906</v>
+        <v>3.295362677844774</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321027</v>
+        <v>3.865338681321026</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.369255621532834</v>
+        <v>-3.482300135516548</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.421024760581495</v>
+        <v>1.375806954988009</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.032710836157448</v>
+        <v>1.082175251852229</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.388709935202845</v>
+        <v>3.418388584619713</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.318223528810306</v>
+        <v>-3.43126804279402</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.436385825908776</v>
+        <v>1.391168020315291</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.083742928879976</v>
+        <v>1.133207344574757</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.414277419074632</v>
+        <v>3.4439560684915</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.2529993476831</v>
+        <v>-3.366043861666814</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.479662902452363</v>
+        <v>1.434445096858878</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.148967110007182</v>
+        <v>1.198431525701963</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.47059933184366</v>
+        <v>3.500277981260528</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.215572327611966</v>
+        <v>-3.32861684159568</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.490594682780097</v>
+        <v>1.445376877186612</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.154218648036364</v>
+        <v>1.203683063731145</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.469711226960449</v>
+        <v>3.499389876377318</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.235683983646675</v>
+        <v>-3.348728497630388</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.483806812697454</v>
+        <v>1.438589007103969</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.165245993033783</v>
+        <v>1.214710408728564</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.477584426290141</v>
+        <v>3.50726307570701</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.18193916921947</v>
+        <v>-3.294983683203184</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.665862509489547</v>
+        <v>1.620644703896061</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.175309302474245</v>
+        <v>1.224773718169026</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.644180182975629</v>
+        <v>3.673858832392498</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.107156908194457</v>
+        <v>-3.220201422178171</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.815888323117369</v>
+        <v>1.770670517523883</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.250091563499258</v>
+        <v>1.299555979194039</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.809162448808454</v>
+        <v>3.838841098225322</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.081072823930649</v>
+        <v>-3.194117337914363</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.818029932836751</v>
+        <v>1.772812127243266</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.250091563499258</v>
+        <v>1.299555979194039</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.800870424822313</v>
+        <v>3.830549074239181</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.993194910821529</v>
+        <v>-3.106239424805243</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.851374293664179</v>
+        <v>1.806156488070693</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.366017205922609</v>
+        <v>1.41548162161739</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.868619005860103</v>
+        <v>3.898297655276972</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.984302449428245</v>
+        <v>-3.097346963411959</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.872485683948284</v>
+        <v>1.827267878354798</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.366017205922609</v>
+        <v>1.41548162161739</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.886173411586895</v>
+        <v>3.915852061003763</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945369</v>
+        <v>3.794424941945368</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.152778566398123</v>
+        <v>-3.265823080381837</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.796950284564916</v>
+        <v>1.751732478971431</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.338069370206028</v>
+        <v>1.387533785900809</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.86125975756153</v>
+        <v>3.890938406978399</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.45497903753654</v>
+        <v>-2.568023551520254</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.057339793297412</v>
+        <v>2.012121987703926</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.267721310835618</v>
+        <v>1.317185726530398</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.800320619127146</v>
+        <v>3.829999268544014</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632639</v>
+        <v>3.78467134563264</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.432257933853387</v>
+        <v>-2.545302447837101</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.057092257267577</v>
+        <v>2.011874451674092</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.267721310835618</v>
+        <v>1.317185726530398</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.79098464162405</v>
+        <v>3.820663291040919</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777676</v>
+        <v>3.783205696777677</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.56145974714743</v>
+        <v>-2.674504261131144</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.164317657801129</v>
+        <v>2.119099852207643</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.138519497541575</v>
+        <v>1.187983913236356</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.872369679498794</v>
+        <v>3.902048328915662</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644416</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.716240753925685</v>
+        <v>-2.829285267909399</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.139483077583473</v>
+        <v>2.094265271989988</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.105151823487099</v>
+        <v>1.15461623918188</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.889426897559755</v>
+        <v>3.919105546976623</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799968</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.709186063710512</v>
+        <v>-2.822230577694226</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.138980309659088</v>
+        <v>2.093762504065602</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.112206513702273</v>
+        <v>1.161670929397054</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.890335067678404</v>
+        <v>3.920013717095273</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.682234839384024</v>
+        <v>-2.795279353367738</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.159766953034425</v>
+        <v>2.11454914744094</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.127086859729992</v>
+        <v>1.176551275424773</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.909269428939777</v>
+        <v>3.938948078356646</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784111</v>
+        <v>3.768052067784112</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.81818784744034</v>
+        <v>-2.931232361424054</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.289488881956858</v>
+        <v>2.244271076363373</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.127086859729992</v>
+        <v>1.176551275424773</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.093372561084736</v>
+        <v>4.123051210501606</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.840595965245212</v>
+        <v>-2.953640479228926</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.272642329737902</v>
+        <v>2.227424524144417</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.127086859729992</v>
+        <v>1.176551275424773</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.08548925598773</v>
+        <v>4.115167905404599</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155036</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.868820200822813</v>
+        <v>-2.981864714806526</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.2634066350565</v>
+        <v>2.218188829463014</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.145063612181301</v>
+        <v>1.194528027876081</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.098329307008153</v>
+        <v>4.128007956425021</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.878261126711342</v>
+        <v>-2.991305640695056</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.315883982422935</v>
+        <v>2.270666176829449</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.267490729724692</v>
+        <v>1.316955145419473</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.228039295256035</v>
+        <v>4.257717944672903</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.930534734046984</v>
+        <v>-3.043579248030698</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.297865634033979</v>
+        <v>2.252647828440494</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.215217122389051</v>
+        <v>1.264681538083832</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.199566225399951</v>
+        <v>4.229244874816819</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347707</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.00686471164789</v>
+        <v>-3.119909225631603</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.265445455887392</v>
+        <v>2.220227650293906</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.215217122389051</v>
+        <v>1.264681538083832</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.197678038293726</v>
+        <v>4.227356687710595</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887751</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.209118431972243</v>
+        <v>-3.322162945955957</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.179364197360513</v>
+        <v>2.134146391767028</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.012963402064697</v>
+        <v>1.062427817759478</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.071146035701976</v>
+        <v>4.100824685118845</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.71289761234307</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.370686857499498</v>
+        <v>-3.483731371483212</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.113170837359763</v>
+        <v>2.067953031766278</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.886180478266818</v>
+        <v>0.9356448939615988</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.993510291633401</v>
+        <v>4.023188941050269</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389353</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.502988149597051</v>
+        <v>-3.616032663580765</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.07332372738666</v>
+        <v>2.028105921793175</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.886180478266818</v>
+        <v>0.9356448939615988</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.00658369849932</v>
+        <v>4.036262347916188</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378396</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.688856460436281</v>
+        <v>-3.801900974419995</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.990981599833908</v>
+        <v>1.945763794240423</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7276148849468703</v>
+        <v>0.7770793006416511</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.903449539290291</v>
+        <v>3.933128188707159</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006979</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.716757247545754</v>
+        <v>-3.829801761529468</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.978345326117121</v>
+        <v>1.933127520523636</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6930179608039355</v>
+        <v>0.7424823764987163</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.881215425931532</v>
+        <v>3.9108940753484</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.839283350248648</v>
+        <v>-3.952327864232362</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.926099329013162</v>
+        <v>1.880881523419677</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5704918581010416</v>
+        <v>0.6199562737958224</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.804464208286994</v>
+        <v>3.834142857703863</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585941</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.069797846434237</v>
+        <v>-4.182842360417951</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.900599490129431</v>
+        <v>1.855381684535945</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3399773619154529</v>
+        <v>0.3894417776102337</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.732861470166145</v>
+        <v>3.762540119583013</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.326518664429061</v>
+        <v>-4.439563178412774</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.938222881933348</v>
+        <v>1.893005076339863</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2315627877716381</v>
+        <v>0.2810272034664189</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.808124444681703</v>
+        <v>3.837803094098572</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.480505082205202</v>
+        <v>-4.593549596188915</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.945608583968532</v>
+        <v>1.900390778375047</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2315627877716381</v>
+        <v>0.2810272034664189</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.877104713827343</v>
+        <v>3.906783363244211</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.429983178377536</v>
+        <v>-4.543027692361249</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.951868547619719</v>
+        <v>1.906650742026234</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2315627877716381</v>
+        <v>0.2810272034664189</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.863155915947464</v>
+        <v>3.892834565364332</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.68245833238526</v>
+        <v>-4.795502846368973</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.862748975072043</v>
+        <v>1.817531169478558</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2315627877716381</v>
+        <v>0.2810272034664189</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.875026405002878</v>
+        <v>3.904705054419746</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.67402853597316</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.975354088864672</v>
+        <v>-5.088398602848385</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.746801206999222</v>
+        <v>1.701583401405737</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2315627877716381</v>
+        <v>0.2810272034664189</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.876236939521821</v>
+        <v>3.90591558893869</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.663509457251949</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.132898160594114</v>
+        <v>-5.245942674577827</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.687905320534767</v>
+        <v>1.642687514941282</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1646609826313636</v>
+        <v>0.2141253983261444</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.840217598664978</v>
+        <v>3.869896248081846</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916205</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.410862556177388</v>
+        <v>-5.5239070701611</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.571797415037647</v>
+        <v>1.526579609444162</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.07504124834587933</v>
+        <v>0.1245056640406601</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.781523610829877</v>
+        <v>3.811202260246746</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830331</v>
+        <v>3.667962306830332</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.527830248816278</v>
+        <v>-5.640874762799991</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.687214394681134</v>
+        <v>1.64199658908765</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.07504124834587933</v>
+        <v>0.1245056640406601</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.943727667528921</v>
+        <v>3.973406316945789</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.612548191037232</v>
+        <v>-5.725592705020945</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.648173855756567</v>
+        <v>1.602956050163082</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.01007478058216704</v>
+        <v>0.03938963511261373</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.887504688135907</v>
+        <v>3.917183337552776</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.75004401586815</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.694483009306115</v>
+        <v>-5.807527523289828</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.625629346017505</v>
+        <v>1.58041154042402</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.02000952616924723</v>
+        <v>0.02945488952553355</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.89177325835215</v>
+        <v>3.921451907769019</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.796459131554522</v>
+        <v>-5.909503645538235</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.593764535574045</v>
+        <v>1.54854672998056</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1219856484176548</v>
+        <v>-0.07252123272287403</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.839513223459008</v>
+        <v>3.869191872875877</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.686452848077301</v>
+        <v>-5.799497362061014</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.629919936209109</v>
+        <v>1.584702130615624</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.09878107650037959</v>
+        <v>-0.04931666080559882</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.845588853853549</v>
+        <v>3.875267503270417</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818524</v>
+        <v>3.785563924818526</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.543393272336376</v>
+        <v>-5.656437786320089</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.691393777227453</v>
+        <v>1.646175971633968</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.09076764991040032</v>
+        <v>-0.04130323421561954</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.854646920529511</v>
+        <v>3.884325569946379</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051791</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.241946546864538</v>
+        <v>-5.354991060848251</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.819233350298724</v>
+        <v>1.774015544705239</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2106790755614369</v>
+        <v>0.2601434912562177</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.04277583869515</v>
+        <v>4.072454488112018</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679627</v>
+        <v>3.812635940679628</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.266536791099722</v>
+        <v>-5.379581305083435</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.810368430357361</v>
+        <v>1.765150624763876</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2106790755614369</v>
+        <v>0.2601434912562177</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.04374701644786</v>
+        <v>4.073425665864728</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474163</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.215498415093202</v>
+        <v>-5.328542929076915</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.831626685139724</v>
+        <v>1.786408879546239</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2106790755614369</v>
+        <v>0.2601434912562177</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.044589920827615</v>
+        <v>4.074268570244484</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969547</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.174359120226571</v>
+        <v>-5.287403634210284</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.867120501960522</v>
+        <v>1.821902696367037</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2518183704280678</v>
+        <v>0.3012827861228485</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.088311596621739</v>
+        <v>4.117990246038607</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700483</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.063752980146969</v>
+        <v>-5.176797494130682</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.727546954116297</v>
+        <v>1.682329148522812</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3624245105076698</v>
+        <v>0.4118889262024505</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.970859276793434</v>
+        <v>4.000537926210303</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077642</v>
+        <v>3.804688961077645</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.194333714677811</v>
+        <v>-5.307378228661524</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.678816704377924</v>
+        <v>1.633598898784439</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2318437759768273</v>
+        <v>0.281308191671608</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.896012880148893</v>
+        <v>3.925691529565762</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833462</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.02983738048685</v>
+        <v>-5.142881894470563</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.729042057130391</v>
+        <v>1.683824251536906</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2318437759768273</v>
+        <v>0.281308191671608</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.880439699224975</v>
+        <v>3.910118348641844</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077631</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.057207313171282</v>
+        <v>-5.170251827154995</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.717281794493049</v>
+        <v>1.672063988899563</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2318437759768273</v>
+        <v>0.281308191671608</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.879627409661405</v>
+        <v>3.909306059078273</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147912</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.067592508061171</v>
+        <v>-5.180637022044884</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.722996495662165</v>
+        <v>1.67777869006868</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2214585810869379</v>
+        <v>0.2709229967817187</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.883265071852544</v>
+        <v>3.912943721269412</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735286</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.086180666783396</v>
+        <v>-5.199225180767109</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.7863982379497</v>
+        <v>1.741180432356215</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2028704223647126</v>
+        <v>0.2523348380594934</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.942949182395633</v>
+        <v>3.972627831812503</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496557</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.086479213479432</v>
+        <v>-5.199523727463145</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.783147830089584</v>
+        <v>1.737930024496099</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2028704223647126</v>
+        <v>0.2523348380594934</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.939818193213933</v>
+        <v>3.969496842630801</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108859</v>
+        <v>3.815643212108862</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.985656079789004</v>
+        <v>-5.098700593772717</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.828007978505147</v>
+        <v>1.782790172911662</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2153346378490664</v>
+        <v>0.2647990535438472</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.951827617443936</v>
+        <v>3.981506266860804</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121468</v>
+        <v>3.807356168121471</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.794874719036597</v>
+        <v>-4.90791923302031</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.904449776284653</v>
+        <v>1.859231970691168</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4061159986014738</v>
+        <v>0.4555804142962546</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.066425687373924</v>
+        <v>4.096104336790792</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906084</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.776357864994777</v>
+        <v>-4.88940237897849</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.891693363638978</v>
+        <v>1.846475558045492</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.419046128026682</v>
+        <v>0.4685105437214628</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.054020610766645</v>
+        <v>4.083699260183513</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.751164680493459</v>
+        <v>-4.864209194477172</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.936737574051563</v>
+        <v>1.891519768458078</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4442393125280004</v>
+        <v>0.4937037282227812</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.104103458079495</v>
+        <v>4.133782107496363</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539898</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.739110553580496</v>
+        <v>-4.852155067564209</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.935245792718186</v>
+        <v>1.890027987124701</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4562934394409632</v>
+        <v>0.505757855135744</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.10502250212871</v>
+        <v>4.134701151545578</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.745733800270854</v>
+        <v>-4.858778314254567</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.934477124226179</v>
+        <v>1.889259318632694</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4496701927506048</v>
+        <v>0.4991346084453856</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.102929184298631</v>
+        <v>4.132607833715499</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382923</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.642853210742262</v>
+        <v>-4.755897724725974</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.988480385915498</v>
+        <v>1.943262580322013</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5525507822791977</v>
+        <v>0.6020151979739785</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.177508563893669</v>
+        <v>4.207187213310537</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760316</v>
+        <v>3.646857607760319</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.666295249922348</v>
+        <v>-4.779339763906061</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.999306240417058</v>
+        <v>1.954088434823572</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5525507822791977</v>
+        <v>0.6020151979739785</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.197711234067263</v>
+        <v>4.227389883484132</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781706</v>
+        <v>3.666767386781709</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.68436775821396</v>
+        <v>-4.797412272197673</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.992077237100413</v>
+        <v>1.946859431506928</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5525507822791977</v>
+        <v>0.6020151979739785</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.197711234067263</v>
+        <v>4.227389883484132</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082835</v>
+        <v>3.670068888082838</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.915541552090592</v>
+        <v>-5.028586066074305</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.859859633143227</v>
+        <v>1.814641827549742</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5525507822791977</v>
+        <v>0.6020151979739785</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.157963147660729</v>
+        <v>4.187641797077599</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.884255531550137</v>
+        <v>-4.99730004553385</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.879396660356349</v>
+        <v>1.834178854762864</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.5838368028196531</v>
+        <v>0.6333012185144339</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.183757378981943</v>
+        <v>4.213436028398812</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677827</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.731230139436852</v>
+        <v>-4.844274653420565</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.039777816774567</v>
+        <v>1.994560011181082</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.7368621949329373</v>
+        <v>0.786326610627718</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.374743613822818</v>
+        <v>4.404422263239686</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073884</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.738367210622143</v>
+        <v>-4.851411724605856</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.224389213208743</v>
+        <v>2.179171407615258</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.7368621949329373</v>
+        <v>0.786326610627718</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.562209838731111</v>
+        <v>4.591888488147979</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.822546110568343</v>
+        <v>3.423889058699156</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.22426874529137</v>
+        <v>3.988556275514219</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.738367210622143</v>
+        <v>-4.851411724605856</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.224389213208743</v>
+        <v>2.179171407615258</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7368621949329373</v>
+        <v>0.786326610627718</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.217332542277738</v>
+        <v>3.981620072500587</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240811.xlsx
+++ b/tame_output/ON/bt/strategyON_20240811.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>38.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>97.3%</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>110.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>124.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-597.3%</t>
+          <t>-617.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>428.1%</t>
+          <t>423.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-646.7%</t>
+          <t>-637.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-239.3%</t>
+          <t>-247.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.3%</t>
+          <t>-157.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-228.8%</t>
+          <t>-248.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-269.3%</t>
+          <t>-151.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-145.4%</t>
+          <t>-152.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-137.6%</t>
+          <t>-149.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.260882186682066</v>
+        <v>-1.459224753477259</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.612210968455291</v>
+        <v>2.532873941737214</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.253873330619843</v>
+        <v>1.05553076382465</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.86924426581377</v>
+        <v>3.750238725736655</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.626950913826719</v>
+        <v>-1.825293480621912</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.458867776903879</v>
+        <v>2.379530750185801</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.88780460347519</v>
+        <v>0.6894620366799974</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.642687328833428</v>
+        <v>3.523681788756312</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.835441695278403</v>
+        <v>-2.033784262073596</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.395809754061973</v>
+        <v>2.316472727343896</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.6793138220235055</v>
+        <v>0.480971255228313</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.537931149701186</v>
+        <v>3.41892560962407</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.082642880043625</v>
+        <v>-2.280985446838818</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.305028030564453</v>
+        <v>2.225691003846376</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.699467175522318</v>
+        <v>0.5011246087271254</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.558121912209042</v>
+        <v>3.439116372131926</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.575027908067722</v>
+        <v>-2.773370474862915</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.109180411398547</v>
+        <v>2.029843384680469</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.2070821474982212</v>
+        <v>0.00873958070302866</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.263797287438316</v>
+        <v>3.1447917473612</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.960208298997795</v>
+        <v>-3.158550865792987</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.953650793839381</v>
+        <v>1.874313767121304</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.2070821474982212</v>
+        <v>0.00873958070302866</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.262339826251179</v>
+        <v>3.143334286174063</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.210078979012376</v>
+        <v>-3.408421545807569</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.855471645288164</v>
+        <v>1.776134618570087</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.2433448673286845</v>
+        <v>0.04500230053349191</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.285866581604073</v>
+        <v>3.166861041526957</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.416590755899398</v>
+        <v>-3.61493332269459</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.768972993189614</v>
+        <v>1.689635966471537</v>
       </c>
       <c r="F1857" t="n">
-        <v>0.036833090441663</v>
+        <v>-0.1615094763535296</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.158065574128118</v>
+        <v>3.039060034051003</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.735934830979899</v>
+        <v>-3.934277397775091</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.643008289857673</v>
+        <v>1.563671263139596</v>
       </c>
       <c r="F1858" t="n">
-        <v>0.036833090441663</v>
+        <v>-0.1615094763535296</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.159838500828378</v>
+        <v>3.040832960751262</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.122144662255674</v>
+        <v>-4.320487229050866</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.474857244814767</v>
+        <v>1.39552021809669</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.05393984927578033</v>
+        <v>-0.2522824160709729</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.091707624465316</v>
+        <v>2.9727020843882</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.356838656388226</v>
+        <v>-4.555181223183419</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.369264422163837</v>
+        <v>1.28992739544576</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.04760358204652515</v>
+        <v>-0.2459461488417177</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.08379415980496</v>
+        <v>2.964788619727844</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.692501303618679</v>
+        <v>-4.890843870413871</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.233579954927621</v>
+        <v>1.154242928209544</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.11553456753543</v>
+        <v>-0.3138771343306225</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.041616160167582</v>
+        <v>2.922610620090466</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.76894563382155</v>
+        <v>-4.967288200616743</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.209489783080714</v>
+        <v>1.130152756362637</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.03508905844176807</v>
+        <v>-0.2334316252369606</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.096371025858021</v>
+        <v>2.977365485780905</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.134073016460297</v>
+        <v>-5.332415583255489</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.062693345031047</v>
+        <v>0.9833563183129694</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3313998427407806</v>
+        <v>-0.5297424095359732</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.917839070284444</v>
+        <v>2.798833530207329</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.542661793640976</v>
+        <v>-5.741004360436168</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8980193781735339</v>
+        <v>0.8186823514554571</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9383311867166516</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.671447347990797</v>
+        <v>2.552441807913681</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.656422205663841</v>
+        <v>-5.854764772459033</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8477006458358489</v>
+        <v>0.7683636191177716</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9383311867166516</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.666632780462257</v>
+        <v>2.547627240385141</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.072814079950838</v>
+        <v>-6.27115664674603</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6791379467299272</v>
+        <v>0.5998009200118499</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9383311867166516</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.664626831071135</v>
+        <v>2.545621290994019</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.433987709767826</v>
+        <v>-6.632330276563018</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5449271854718107</v>
+        <v>0.4655901587537339</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9383311867166516</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.674885521739814</v>
+        <v>2.555879981662698</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.777246229410845</v>
+        <v>-6.975588796206037</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4037233427602986</v>
+        <v>0.3243863160422218</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9383311867166516</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.670985086885509</v>
+        <v>2.551979546808393</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.825449046653189</v>
+        <v>-7.023791613448381</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3828471359183618</v>
+        <v>0.303510109200285</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9383311867166516</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.669390006940509</v>
+        <v>2.550384466863394</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.122110388463386</v>
+        <v>-7.320452955258578</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2679615751234912</v>
+        <v>0.1886245484054143</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-1.00707432245053</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.631923101429391</v>
+        <v>2.512917561352275</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.308830096772689</v>
+        <v>-7.507172663567881</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1892473872653668</v>
+        <v>0.10991036054729</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-1.00707432245053</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.627896796894988</v>
+        <v>2.508891256817872</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.69183148551532</v>
+        <v>-7.890174052310512</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.03594473044673041</v>
+        <v>-0.04339229627134644</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-1.00707432245053</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.627794695573404</v>
+        <v>2.508789155496288</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.696317930716709</v>
+        <v>-7.894660497511901</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.03672166833760526</v>
+        <v>-0.04261535838047203</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-1.011560767651919</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.627674344424</v>
+        <v>2.508668804346885</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.055848253220711</v>
+        <v>-8.254190820015904</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1017401573659455</v>
+        <v>-0.1810771840840228</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-1.011560767651919</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.63302464772205</v>
+        <v>2.514019107644935</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.106197316674933</v>
+        <v>-8.304539883470126</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1139637627904571</v>
+        <v>-0.1933007895085339</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8635672643109484</v>
+        <v>-1.061909831106141</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.610731229606695</v>
+        <v>2.491725689529579</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.203816594096329</v>
+        <v>-8.402159160891522</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1499697231372465</v>
+        <v>-0.2293067498553234</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9611865417323451</v>
+        <v>-1.159529108527537</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.555201413775626</v>
+        <v>2.43619587369851</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.257888093604688</v>
+        <v>-8.45623066039988</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168704766619018</v>
+        <v>-0.2480417933370949</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.015258041240704</v>
+        <v>-1.213600608035897</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.525652070392182</v>
+        <v>2.406646530315067</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.660488835729744</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.3242318663503978</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.341239552649886</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.335576360665315</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.694141674238217</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.3332104472693511</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.441652920566923</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.279810894399529</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.422329275775576</v>
+        <v>-8.620671842570768</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2091137863908736</v>
+        <v>-0.2884508131089505</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.169840522104282</v>
+        <v>-1.368183088899475</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.458270034970535</v>
+        <v>2.33926449489342</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.597453693162119</v>
+        <v>-8.795796259957312</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.264608332597974</v>
+        <v>-0.3439453593160513</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.543307506286019</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.367750605286126</v>
+        <v>2.24874506520901</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.831905787176609</v>
+        <v>-9.030248353971801</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3656083351053661</v>
+        <v>-0.4449453618234429</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.543307506286019</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36053144038453</v>
+        <v>2.241525900307414</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.936280518203056</v>
+        <v>-9.134623084998248</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4140304182899208</v>
+        <v>-0.4933674450079977</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.449339670517272</v>
+        <v>-1.647682237312464</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.291234410994686</v>
+        <v>2.172228870917571</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.09879398390164</v>
+        <v>-9.297136550696832</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.477920014730798</v>
+        <v>-0.5572570414488753</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.546973100935959</v>
+        <v>-1.745315667731151</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.23377014258203</v>
+        <v>2.114764602504914</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.224830777269929</v>
+        <v>-9.423173344065122</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5256410034489991</v>
+        <v>-0.6049780301670764</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.720064044921409</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.25161484489699</v>
+        <v>2.132609304819875</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.167759005373998</v>
+        <v>-9.366101572169191</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4988219590042262</v>
+        <v>-0.5781589857223031</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.720064044921409</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.255605180583391</v>
+        <v>2.136599640506275</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.309430847098119</v>
+        <v>-9.507773413893311</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.556965922592616</v>
+        <v>-0.6363029493106929</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.720064044921409</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.254129953684649</v>
+        <v>2.135124413607534</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.259840002673284</v>
+        <v>-9.458182569468477</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5220761746578098</v>
+        <v>-0.6014132013758871</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.472130633701382</v>
+        <v>-1.670473200496575</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.298937870504422</v>
+        <v>2.179932330427306</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.110921668201428</v>
+        <v>-9.30926423499662</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4755599745157504</v>
+        <v>-0.5548970012338272</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.440881042966209</v>
+        <v>-1.639223609761402</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.304636491298843</v>
+        <v>2.185630951221727</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.885076515482016</v>
+        <v>-9.08341908227721</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3756428403917771</v>
+        <v>-0.4549798671098544</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.597296934174238</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.33937156968735</v>
+        <v>2.220366029610234</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.760497859144424</v>
+        <v>-8.958840425939618</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3246722333006811</v>
+        <v>-0.4040092600187588</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.597296934174238</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.340510714243409</v>
+        <v>2.221505174166293</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-9.011735713983905</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.4225336010743659</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.592341588085792</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.346117696058584</v>
+        <v>2.227112155981468</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.939602538696024</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.3879466267205771</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.592341588085792</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351851400297221</v>
+        <v>2.232845860220105</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.868236146086376</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.3691373320705833</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.520975195476144</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.384933973469144</v>
+        <v>2.265928433392029</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.774777112101152</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.341637199789401</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.520975195476144</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.375050492156237</v>
+        <v>2.256044952079121</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.76412393054772</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.339210487667402</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.520975195476144</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.373215931656863</v>
+        <v>2.254210391579747</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.66621689187123</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.3003479871702668</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.254646878820395</v>
+        <v>-1.452989445615588</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.413707066599736</v>
+        <v>2.29470152652262</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.642263350895272</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.2900980646343898</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.230693337844438</v>
+        <v>-1.42903590463963</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.428747697330804</v>
+        <v>2.309742157253688</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.378203412572475</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.1977344054670231</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-1.164975966316834</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.454917804085614</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.472781222272443</v>
+        <v>-7.671123789067637</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1616474369926886</v>
+        <v>0.08231041027461128</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-1.164975966316834</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.452130770425313</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.432596923906252</v>
+        <v>-7.630939490701446</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1780647802270061</v>
+        <v>0.09872775350892882</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-1.124791667950643</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.476584973332869</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.26919705296689</v>
+        <v>-7.467539619762084</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.242791549823508</v>
+        <v>0.1634545231054307</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.9613917970112806</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.573991717117243</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.035715830737291</v>
+        <v>-7.234058397532485</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3441084675532</v>
+        <v>0.2647714408351223</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.7279105747816821</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.722004879292855</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.886049439729776</v>
+        <v>-7.08439200652497</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4010828136432467</v>
+        <v>0.3217457869251694</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.6350070835391461</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.774854763725417</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.75377396609889</v>
+        <v>-6.952116532894084</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4493604898426287</v>
+        <v>0.3700234631245509</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.5027316099082595</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>2.849587534650976</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.598035633539148</v>
+        <v>-6.796378200334342</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.514470883554162</v>
+        <v>0.4351338568360843</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.3469932773485179</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>2.945845594874458</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.513070966809828</v>
+        <v>-6.711413533605022</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5613630914695489</v>
+        <v>0.4820260647514711</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>-0.2620286106191984</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.009730736135708</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.618660956582932</v>
+        <v>-6.817003523378126</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3911511659610882</v>
+        <v>0.3118141392430105</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.3676186003923027</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.818400812672627</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.637395858701529</v>
+        <v>-6.835738425496723</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4322015469907359</v>
+        <v>0.3528645202726581</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1748720432572415</v>
+        <v>-0.373214610052434</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.98259308883075</v>
+        <v>2.863587548753634</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.48945581729393</v>
+        <v>-6.687798384089124</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.371498640865608</v>
+        <v>0.2921616141475303</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.154551127348684</v>
+        <v>-0.3528936941438764</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.874906715687717</v>
+        <v>2.755901175610601</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.436486295039941</v>
+        <v>-6.634828861835135</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3839724635137252</v>
+        <v>0.3046354367956474</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1015816050946951</v>
+        <v>-0.2999241718898876</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.897974442786632</v>
+        <v>2.778968902709517</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.270698099079651</v>
+        <v>-6.469040665874845</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4433271298027481</v>
+        <v>0.3639901030846708</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1015816050946951</v>
+        <v>-0.2999241718898876</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.891013830691539</v>
+        <v>2.772008290614424</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.237334892600882</v>
+        <v>-6.435677459396076</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4711347667753989</v>
+        <v>0.3917977400573212</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1015816050946951</v>
+        <v>-0.2999241718898876</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.905476185072682</v>
+        <v>2.786470644995567</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.12907575547836</v>
+        <v>-6.327418322273554</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5089705420836026</v>
+        <v>0.4296335153655249</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1015816050946951</v>
+        <v>-0.2999241718898876</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.900008305531877</v>
+        <v>2.781002765454762</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.005784620661229</v>
+        <v>-6.204127187456423</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5557850900210317</v>
+        <v>0.476448063302954</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.02170952972243539</v>
+        <v>-0.1766330370727571</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.971481080432732</v>
+        <v>2.852475540355617</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.953087753529938</v>
+        <v>-6.151430320325132</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5845648151108738</v>
+        <v>0.505227788392796</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.07440639685372658</v>
+        <v>-0.1239361699414659</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.010800178948832</v>
+        <v>2.891794638871717</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.709322311546494</v>
+        <v>-5.907664878341688</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6778517002513018</v>
+        <v>0.5985146735332245</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.07440639685372658</v>
+        <v>-0.1239361699414659</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.006580887295883</v>
+        <v>2.887575347218768</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.619546639170022</v>
+        <v>-5.817889205965216</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7158862831219071</v>
+        <v>0.6365492564038293</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1360058417680366</v>
+        <v>-0.06233672502715587</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.045664868164485</v>
+        <v>2.926659328087369</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.532205174899443</v>
+        <v>-5.568038812016141</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7435649438138405</v>
+        <v>0.7292314889671614</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1360058417680366</v>
+        <v>-0.06233672502715587</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.038406943148187</v>
+        <v>2.919401403071071</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.35631308243201</v>
+        <v>-5.392146719548709</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8175209043214626</v>
+        <v>0.8031874494747826</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1360058417680366</v>
+        <v>-0.06233672502715587</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.042006066668836</v>
+        <v>2.92300052659172</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.184866619409546</v>
+        <v>-5.220700256526245</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8994269955850016</v>
+        <v>0.885093540738322</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3074523047904997</v>
+        <v>0.1091097379953073</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.158201450536867</v>
+        <v>3.039195910459752</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.110577053671207</v>
+        <v>-5.146410690787906</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9281632994966342</v>
+        <v>0.9138298446499546</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.381741870528839</v>
+        <v>0.1833993037336465</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.201795667596168</v>
+        <v>3.082790127519052</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.046941311437273</v>
+        <v>-5.082774948553972</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9583123974445251</v>
+        <v>0.9439789425978455</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4453776127627735</v>
+        <v>0.2470350459675811</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.244671913990846</v>
+        <v>3.12566637391373</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.935514552111353</v>
+        <v>-4.971348189228052</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9840773599586889</v>
+        <v>0.9697439051120091</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4453776127627735</v>
+        <v>0.2470350459675811</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.225866172774642</v>
+        <v>3.106860632697526</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.946017175176642</v>
+        <v>-4.981850812293341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9816193873574508</v>
+        <v>0.967285932510771</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4348749896974847</v>
+        <v>0.2365324229022922</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.221307675560346</v>
+        <v>3.10230213548323</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.873774607005447</v>
+        <v>-4.909608244122146</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.014445728460749</v>
+        <v>1.000112273614069</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4348749896974847</v>
+        <v>0.2365324229022922</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.225236989395166</v>
+        <v>3.10623144931805</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.856060920127582</v>
+        <v>-4.891894557244281</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.022209787129235</v>
+        <v>1.007876332282555</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4380563185944015</v>
+        <v>0.239713751799209</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.227824370650656</v>
+        <v>3.10881883057354</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.747256034647855</v>
+        <v>-4.783089671764554</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.062729812541119</v>
+        <v>1.04839635769444</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4380563185944015</v>
+        <v>0.239713751799209</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.224822441870649</v>
+        <v>3.105816901793534</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.527235236610844</v>
+        <v>-4.563068873727543</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.152317168766538</v>
+        <v>1.137983713919858</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5792761636623818</v>
+        <v>0.3809335968671893</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.311133385922052</v>
+        <v>3.192127845844936</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.394367547547566</v>
+        <v>-4.430201184664265</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.221358427193672</v>
+        <v>1.207024972346992</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5792761636623818</v>
+        <v>0.3809335968671893</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.327027568723875</v>
+        <v>3.208022028646759</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.274194464183068</v>
+        <v>-4.310028101299767</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.270573504979773</v>
+        <v>1.256240050133094</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6994492470268807</v>
+        <v>0.5011066802316881</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.400277263182876</v>
+        <v>3.28127172310576</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.13894110285309</v>
+        <v>-4.17477473996979</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.334762952073204</v>
+        <v>1.320429497226524</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8347026083568578</v>
+        <v>0.6363600415616653</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.491517382542302</v>
+        <v>3.372511842465187</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.198815930210783</v>
+        <v>-4.234649567327482</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.296850512531553</v>
+        <v>1.282517057684873</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7748277809991657</v>
+        <v>0.5764852142039731</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.441629977529113</v>
+        <v>3.322624437451998</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.078995699299946</v>
+        <v>-4.114829336416645</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.360067774130096</v>
+        <v>1.345734319283417</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7748277809991657</v>
+        <v>0.5764852142039731</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.456919146763322</v>
+        <v>3.337913606686206</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.081465405761752</v>
+        <v>-4.117299042878451</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.266724090867815</v>
+        <v>1.252390636021136</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7723580745373595</v>
+        <v>0.5740155077421669</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.363081522208679</v>
+        <v>3.244075982131564</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.149835592085762</v>
+        <v>-4.185669229202461</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.158637877823513</v>
+        <v>1.144304422976833</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7816337735735744</v>
+        <v>0.5832912067783819</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.28790880311571</v>
+        <v>3.168903263038594</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.163623644932809</v>
+        <v>-4.199457282049508</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.143559365316585</v>
+        <v>1.129225910469906</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7816337735735744</v>
+        <v>0.5832912067783819</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.278345511747601</v>
+        <v>3.159339971670486</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.219143720825398</v>
+        <v>-4.254977357942098</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.258382171651752</v>
+        <v>1.244048716805072</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7816337735735744</v>
+        <v>0.5832912067783819</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.415376348439803</v>
+        <v>3.296370808362687</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.043669461032929</v>
+        <v>-4.079503098149628</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.333139107560527</v>
+        <v>1.318805652713848</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7816337735735744</v>
+        <v>0.5832912067783819</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.419943580431591</v>
+        <v>3.300938040354476</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.154605713674178</v>
+        <v>-4.190439350790877</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.264506635265235</v>
+        <v>1.250173180418555</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7816337735735744</v>
+        <v>0.5832912067783819</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.395685609192798</v>
+        <v>3.276680069115683</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.120942168201895</v>
+        <v>-4.156775805318595</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.206510366855598</v>
+        <v>1.192176912008918</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8152973190458563</v>
+        <v>0.6169547522506638</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.344422049877617</v>
+        <v>3.225416509800501</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.061089548998172</v>
+        <v>-4.096923186114871</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.240623800969219</v>
+        <v>1.22629034612254</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8152973190458563</v>
+        <v>0.6169547522506638</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.35459443630975</v>
+        <v>3.235588896232634</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.974846085971794</v>
+        <v>-4.010679723088494</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.270067456753631</v>
+        <v>1.255734001906951</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8152973190458563</v>
+        <v>0.6169547522506638</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.34954070688361</v>
+        <v>3.230535166806494</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.020152905370774</v>
+        <v>-4.055986542487473</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.243720504438564</v>
+        <v>1.229387049591885</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7744871560366255</v>
+        <v>0.576144589241433</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.316830384522597</v>
+        <v>3.197824844445481</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.049186010073075</v>
+        <v>-4.085019647189775</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.232659135590745</v>
+        <v>1.218325680744066</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7744871560366255</v>
+        <v>0.576144589241433</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.317382257555698</v>
+        <v>3.198376717478583</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.956375528622216</v>
+        <v>-3.992209165738915</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.199056020062455</v>
+        <v>1.184722565215775</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8672976374874849</v>
+        <v>0.6689550706922923</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.30234123831758</v>
+        <v>3.183335698240464</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.000764997951643</v>
+        <v>-4.036598635068343</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.183173708255285</v>
+        <v>1.168840253408605</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8229081681580572</v>
+        <v>0.6245656013628647</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.277581032644524</v>
+        <v>3.158575492567408</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.117306603056987</v>
+        <v>-4.153140240173686</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.13163277472487</v>
+        <v>1.117299319878191</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7063665630527145</v>
+        <v>0.5080239962575219</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.202731778093042</v>
+        <v>3.083726238015926</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.157230697639559</v>
+        <v>-4.193064334756258</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.121154432722509</v>
+        <v>1.106820977875829</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7063665630527145</v>
+        <v>0.5080239962575219</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.208223073923708</v>
+        <v>3.089217533846593</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.185011095540911</v>
+        <v>-4.220844732657611</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.121539475330507</v>
+        <v>1.107206020483827</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6785861651513614</v>
+        <v>0.4802435983561689</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.203052036951436</v>
+        <v>3.08404649687432</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.30339176827105</v>
+        <v>-4.339225405387749</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9125429262391047</v>
+        <v>0.8982094713924251</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6113683130003852</v>
+        <v>0.4130257462051927</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.001077045661503</v>
+        <v>2.882071505584388</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.412005846714381</v>
+        <v>-4.44783948383108</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.989246955580978</v>
+        <v>0.9749135007342982</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6113683130003852</v>
+        <v>0.4130257462051927</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.121226706380709</v>
+        <v>3.002221166303593</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.376596808466238</v>
+        <v>-4.412430445582937</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.017923596982558</v>
+        <v>1.003590142135878</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6113683130003852</v>
+        <v>0.4130257462051927</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.135739732483032</v>
+        <v>3.016734192405916</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.338213145908087</v>
+        <v>-4.374046783024786</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.030696503348187</v>
+        <v>1.016363048501507</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6497519755585364</v>
+        <v>0.4514094087633438</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.156189371360291</v>
+        <v>3.037183831283176</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.161096815872921</v>
+        <v>-4.19693045298962</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.098272064207555</v>
+        <v>1.083938609360876</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6497519755585364</v>
+        <v>0.4514094087633438</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.152918400205593</v>
+        <v>3.033912860128478</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.206189060706467</v>
+        <v>-4.242022697823166</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.08091855803605</v>
+        <v>1.066585103189371</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5878559323891466</v>
+        <v>0.3895133655939541</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.116464166065872</v>
+        <v>2.997458625988757</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.026813639467699</v>
+        <v>-4.062647276584398</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.146455701837972</v>
+        <v>1.132122246991292</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7446326905598653</v>
+        <v>0.5462901237646727</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.204317196274718</v>
+        <v>3.085311656197602</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.071827852988305</v>
+        <v>-4.107661490105004</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.109257471761319</v>
+        <v>1.094924016914639</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7142837952452606</v>
+        <v>0.5159412284500681</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.166915314417545</v>
+        <v>3.047909774340429</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.33883236326074</v>
+        <v>-4.374666000377439</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.008147229991291</v>
+        <v>0.9938137751446112</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5199207572023121</v>
+        <v>0.3215781904071195</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.055989053930722</v>
+        <v>2.936983513853606</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.440030144697912</v>
+        <v>-4.475863781814612</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9668720393129233</v>
+        <v>0.9525385844662435</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4515119436569929</v>
+        <v>0.2531693768618003</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.014147687700031</v>
+        <v>2.895142147622916</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.4335191780836</v>
+        <v>-4.469352815200299</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9670763875129651</v>
+        <v>0.9527429326662853</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4515119436569929</v>
+        <v>0.2531693768618003</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.011747649254348</v>
+        <v>2.892742109177233</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.414481050376303</v>
+        <v>-4.450314687493002</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9712163578041288</v>
+        <v>0.9568829029574493</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3933283323257984</v>
+        <v>0.1949857655306058</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.973362201663877</v>
+        <v>2.854356661586761</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.466996852651123</v>
+        <v>-4.502830489767822</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.069504438528391</v>
+        <v>1.055170983681711</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3933283323257984</v>
+        <v>0.1949857655306058</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.092656603298067</v>
+        <v>2.973651063220951</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.480863613985041</v>
+        <v>-4.51669725110174</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.064791062980957</v>
+        <v>1.050457608134278</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3554704155919755</v>
+        <v>0.1571278487967828</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.070775182243906</v>
+        <v>2.951769642166791</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.436059442445111</v>
+        <v>-4.47189307956181</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.088721261993855</v>
+        <v>1.074387807147176</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3554704155919755</v>
+        <v>0.1571278487967828</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.076783712640832</v>
+        <v>2.957778172563717</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.288316472210108</v>
+        <v>-4.324150109326808</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.045768671365056</v>
+        <v>1.031435216518376</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5232777728268586</v>
+        <v>0.324935206031666</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.075418348258962</v>
+        <v>2.956412808181846</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.372137693484807</v>
+        <v>-4.407971330601506</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.015033804386658</v>
+        <v>1.000700349539978</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5232777728268586</v>
+        <v>0.324935206031666</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.078211969790443</v>
+        <v>2.959206429713327</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.365984987432022</v>
+        <v>-4.401818624548722</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.01815723519943</v>
+        <v>1.00382378035275</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5294304788796429</v>
+        <v>0.3310879120844503</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.082565941813772</v>
+        <v>2.963560401736656</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.382794285582524</v>
+        <v>-4.418627922699224</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.010513992679339</v>
+        <v>0.9961805378326594</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5126211807291412</v>
+        <v>0.3142786139339486</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.071560839663581</v>
+        <v>2.952555299586465</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.320496286806402</v>
+        <v>-4.356329923923101</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.101768745986609</v>
+        <v>1.087435291139929</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5579154450035833</v>
+        <v>0.3595728782083907</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.165072952025067</v>
+        <v>3.046067411947952</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.118706089141244</v>
+        <v>-4.154539726257943</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9847768267667991</v>
+        <v>0.9704433719201195</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7559336371727376</v>
+        <v>0.5575910703775451</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.086175869040687</v>
+        <v>2.967170328963571</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.169592801827439</v>
+        <v>-4.205426438944138</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.034712374014497</v>
+        <v>1.020378919167817</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7050469244865432</v>
+        <v>0.5067043576913506</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.125934073751146</v>
+        <v>3.00692853367403</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.082982059177632</v>
+        <v>-4.118815696294331</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.083984407190463</v>
+        <v>1.069650952343783</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7836726556917014</v>
+        <v>0.5853300888965088</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.187737248590284</v>
+        <v>3.068731708513168</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.143191357182917</v>
+        <v>-4.179024994299616</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.05843666881302</v>
+        <v>1.044103213966341</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7234633576864169</v>
+        <v>0.5251207908912243</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.150147650611785</v>
+        <v>3.031142110534669</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.06676931075099</v>
+        <v>-4.102602947867689</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.08749710542572</v>
+        <v>1.07316365057904</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7234633576864169</v>
+        <v>0.5251207908912243</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.148639268651714</v>
+        <v>3.029633728574598</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.022396179112421</v>
+        <v>-4.058229816229121</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.105109225516584</v>
+        <v>1.090775770669904</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7678364893249855</v>
+        <v>0.5694939225297929</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.175126015070291</v>
+        <v>3.056120474993175</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.044876529971306</v>
+        <v>-4.080710167088005</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.09051087931162</v>
+        <v>1.07617742446494</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7678364893249855</v>
+        <v>0.5694939225297929</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.169519809208881</v>
+        <v>3.050514269131765</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.99722079941025</v>
+        <v>-4.03305443652695</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.115954928563847</v>
+        <v>1.101621473717167</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8154922198860411</v>
+        <v>0.6171496530908486</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.20449500457332</v>
+        <v>3.085489464496204</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.896702640911496</v>
+        <v>-3.932536278028195</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.161054565338074</v>
+        <v>1.146721110491394</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9160103783847957</v>
+        <v>0.7176678115896031</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.269698273047297</v>
+        <v>3.150692732970181</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.880797311479143</v>
+        <v>-3.916630948595842</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.154171369586887</v>
+        <v>1.139837914740207</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8368977176755568</v>
+        <v>0.6385551508803642</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.208985349097626</v>
+        <v>3.08997980902051</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.835958909870745</v>
+        <v>-3.871792546987444</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.176204432840875</v>
+        <v>1.161870977994195</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8414411506204262</v>
+        <v>0.6430985838252337</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.215809111475176</v>
+        <v>3.09680357139806</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.855457366112753</v>
+        <v>-3.891291003229453</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.172565989975149</v>
+        <v>1.15823253512847</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7933565093405219</v>
+        <v>0.5950139425453294</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.191119266338311</v>
+        <v>3.072113726261196</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.811254529026853</v>
+        <v>-3.847088166143552</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.196126727337347</v>
+        <v>1.181793272490667</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8375593464264224</v>
+        <v>0.6392167796312298</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.223520571117689</v>
+        <v>3.104515031040573</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.848233556690296</v>
+        <v>-3.884067193806995</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.179745116741217</v>
+        <v>1.165411661894537</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8745332482177529</v>
+        <v>0.6761906814225603</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.244114912661735</v>
+        <v>3.125109372584619</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.689942139151024</v>
+        <v>-3.725775776267723</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.294309448939966</v>
+        <v>1.279975994093286</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8745332482177529</v>
+        <v>0.6761906814225603</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.295362677844774</v>
+        <v>3.176357137767659</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.482300135516548</v>
+        <v>-3.518133772633247</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.375806954988009</v>
+        <v>1.36147350014133</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.082175251852229</v>
+        <v>0.8838326850570365</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.418388584619713</v>
+        <v>3.299383044542598</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.43126804279402</v>
+        <v>-3.467101679910719</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.391168020315291</v>
+        <v>1.376834565468611</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.133207344574757</v>
+        <v>0.9348647777795644</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.4439560684915</v>
+        <v>3.324950528414385</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.366043861666814</v>
+        <v>-3.401877498783513</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.434445096858878</v>
+        <v>1.420111642012198</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.198431525701963</v>
+        <v>1.00008895890677</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.500277981260528</v>
+        <v>3.381272441183413</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.32861684159568</v>
+        <v>-3.364450478712379</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.445376877186612</v>
+        <v>1.431043422339932</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.203683063731145</v>
+        <v>1.005340496935952</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.499389876377318</v>
+        <v>3.380384336300202</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.348728497630388</v>
+        <v>-3.384562134747088</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.438589007103969</v>
+        <v>1.424255552257289</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.214710408728564</v>
+        <v>1.016367841933371</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.50726307570701</v>
+        <v>3.388257535629894</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.294983683203184</v>
+        <v>-3.330817320319883</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.620644703896061</v>
+        <v>1.606311249049382</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.224773718169026</v>
+        <v>1.026431151373833</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.673858832392498</v>
+        <v>3.554853292315382</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.220201422178171</v>
+        <v>-3.25603505929487</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.770670517523883</v>
+        <v>1.756337062677204</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.299555979194039</v>
+        <v>1.101213412398846</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.838841098225322</v>
+        <v>3.719835558148207</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.194117337914363</v>
+        <v>-3.229950975031062</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.772812127243266</v>
+        <v>1.758478672396586</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.299555979194039</v>
+        <v>1.101213412398846</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.830549074239181</v>
+        <v>3.711543534162066</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.106239424805243</v>
+        <v>-3.142073061921942</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.806156488070693</v>
+        <v>1.791823033224014</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.41548162161739</v>
+        <v>1.217139054822197</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.898297655276972</v>
+        <v>3.779292115199856</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.097346963411959</v>
+        <v>-3.133180600528658</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.827267878354798</v>
+        <v>1.812934423508118</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.41548162161739</v>
+        <v>1.217139054822197</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.915852061003763</v>
+        <v>3.796846520926647</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.265823080381837</v>
+        <v>-3.301656717498536</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.751732478971431</v>
+        <v>1.737399024124751</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.387533785900809</v>
+        <v>1.189191219105616</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.890938406978399</v>
+        <v>3.771932866901283</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.568023551520254</v>
+        <v>-2.603857188636953</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.012121987703926</v>
+        <v>1.997788532857246</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.317185726530398</v>
+        <v>1.118843159735205</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.829999268544014</v>
+        <v>3.710993728466898</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.545302447837101</v>
+        <v>-2.5811360849538</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.011874451674092</v>
+        <v>1.997540996827412</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.317185726530398</v>
+        <v>1.118843159735205</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.820663291040919</v>
+        <v>3.701657750963803</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.674504261131144</v>
+        <v>-2.710337898247843</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.119099852207643</v>
+        <v>2.104766397360964</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.187983913236356</v>
+        <v>0.9896413464411631</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.902048328915662</v>
+        <v>3.783042788838546</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.829285267909399</v>
+        <v>-2.865118905026098</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.094265271989988</v>
+        <v>2.079931817143308</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.15461623918188</v>
+        <v>0.9562736723866869</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.919105546976623</v>
+        <v>3.800100006899507</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.822230577694226</v>
+        <v>-2.858064214810925</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.093762504065602</v>
+        <v>2.079429049218923</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.161670929397054</v>
+        <v>0.9633283626018607</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.920013717095273</v>
+        <v>3.801008177018157</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.795279353367738</v>
+        <v>-2.831112990484437</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.11454914744094</v>
+        <v>2.10021569259426</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.176551275424773</v>
+        <v>0.9782087086295799</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.938948078356646</v>
+        <v>3.81994253827953</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.931232361424054</v>
+        <v>-2.967065998540753</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.244271076363373</v>
+        <v>2.229937621516693</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.176551275424773</v>
+        <v>0.9782087086295799</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.123051210501606</v>
+        <v>4.00404567042449</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.953640479228926</v>
+        <v>-2.989474116345625</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.227424524144417</v>
+        <v>2.213091069297737</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.176551275424773</v>
+        <v>0.9782087086295799</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.115167905404599</v>
+        <v>3.996162365327483</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.981864714806526</v>
+        <v>-3.017698351923225</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.218188829463014</v>
+        <v>2.203855374616334</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.194528027876081</v>
+        <v>0.9961854610808885</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.128007956425021</v>
+        <v>4.009002416347905</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.991305640695056</v>
+        <v>-3.027139277811755</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.270666176829449</v>
+        <v>2.25633272198277</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.316955145419473</v>
+        <v>1.11861257862428</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.257717944672903</v>
+        <v>4.138712404595787</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.043579248030698</v>
+        <v>-3.079412885147397</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.252647828440494</v>
+        <v>2.238314373593814</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.264681538083832</v>
+        <v>1.066338971288639</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.229244874816819</v>
+        <v>4.110239334739703</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.119909225631603</v>
+        <v>-3.155742862748303</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.220227650293906</v>
+        <v>2.205894195447227</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.264681538083832</v>
+        <v>1.066338971288639</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.227356687710595</v>
+        <v>4.108351147633479</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.322162945955957</v>
+        <v>-3.357996583072656</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.134146391767028</v>
+        <v>2.119812936920348</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.062427817759478</v>
+        <v>0.8640852509642851</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.100824685118845</v>
+        <v>3.981819145041729</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.483731371483212</v>
+        <v>-3.519565008599911</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.067953031766278</v>
+        <v>2.053619576919598</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9356448939615988</v>
+        <v>0.7373023271664058</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.023188941050269</v>
+        <v>3.904183400973154</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.616032663580765</v>
+        <v>-3.651866300697464</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.028105921793175</v>
+        <v>2.013772466946495</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9356448939615988</v>
+        <v>0.7373023271664058</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.036262347916188</v>
+        <v>3.917256807839072</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.801900974419995</v>
+        <v>-3.837734611536694</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.945763794240423</v>
+        <v>1.931430339393743</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7770793006416511</v>
+        <v>0.5787367338464581</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.933128188707159</v>
+        <v>3.814122648630043</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.829801761529468</v>
+        <v>-3.865635398646167</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.933127520523636</v>
+        <v>1.918794065676956</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7424823764987163</v>
+        <v>0.5441398097035233</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.9108940753484</v>
+        <v>3.791888535271284</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.952327864232362</v>
+        <v>-3.988161501349061</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.880881523419677</v>
+        <v>1.866548068572997</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6199562737958224</v>
+        <v>0.4216137070006294</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.834142857703863</v>
+        <v>3.715137317626747</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.182842360417951</v>
+        <v>-4.21867599753465</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.855381684535945</v>
+        <v>1.841048229689266</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3894417776102337</v>
+        <v>0.1910992108150407</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.762540119583013</v>
+        <v>3.643534579505897</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.439563178412774</v>
+        <v>-4.475396815529473</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.893005076339863</v>
+        <v>1.878671621493183</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2810272034664189</v>
+        <v>0.08268463667122583</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.837803094098572</v>
+        <v>3.718797554021456</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.593549596188915</v>
+        <v>-4.629383233305614</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.900390778375047</v>
+        <v>1.886057323528367</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2810272034664189</v>
+        <v>0.08268463667122583</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.906783363244211</v>
+        <v>3.787777823167096</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.543027692361249</v>
+        <v>-4.578861329477948</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.906650742026234</v>
+        <v>1.892317287179554</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2810272034664189</v>
+        <v>0.08268463667122583</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.892834565364332</v>
+        <v>3.773829025287216</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.795502846368973</v>
+        <v>-4.831336483485672</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.817531169478558</v>
+        <v>1.803197714631879</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2810272034664189</v>
+        <v>0.08268463667122583</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.904705054419746</v>
+        <v>3.78569951434263</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.088398602848385</v>
+        <v>-5.124232239965084</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.701583401405737</v>
+        <v>1.687249946559057</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2810272034664189</v>
+        <v>0.08268463667122583</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.90591558893869</v>
+        <v>3.786910048861574</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.245942674577827</v>
+        <v>-5.281776311694526</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.642687514941282</v>
+        <v>1.628354060094602</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2141253983261444</v>
+        <v>0.01578283153095134</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.869896248081846</v>
+        <v>3.75089070800473</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.5239070701611</v>
+        <v>-5.5597407072778</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.526579609444162</v>
+        <v>1.512246154597482</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1245056640406601</v>
+        <v>-0.07383690275453292</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.811202260246746</v>
+        <v>3.69219672016963</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.640874762799991</v>
+        <v>-5.676708399916691</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.64199658908765</v>
+        <v>1.62766313424097</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1245056640406601</v>
+        <v>-0.07383690275453292</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.973406316945789</v>
+        <v>3.854400776868673</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.725592705020945</v>
+        <v>-5.761426342137644</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.602956050163082</v>
+        <v>1.588622595316403</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.03938963511261373</v>
+        <v>-0.1589529316825793</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.917183337552776</v>
+        <v>3.79817779747566</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.807527523289828</v>
+        <v>-5.843361160406527</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.58041154042402</v>
+        <v>1.56607808557734</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.02945488952553355</v>
+        <v>-0.1688876772696595</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.921451907769019</v>
+        <v>3.802446367691903</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.909503645538235</v>
+        <v>-5.945337282654934</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.54854672998056</v>
+        <v>1.53421327513388</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.07252123272287403</v>
+        <v>-0.270863799518067</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.869191872875877</v>
+        <v>3.750186332798761</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.799497362061014</v>
+        <v>-5.835330999177713</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.584702130615624</v>
+        <v>1.570368675768944</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.04931666080559882</v>
+        <v>-0.2476592276007918</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.875267503270417</v>
+        <v>3.756261963193301</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.656437786320089</v>
+        <v>-5.692271423436788</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.646175971633968</v>
+        <v>1.631842516787288</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.04130323421561954</v>
+        <v>-0.2396458010108126</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.884325569946379</v>
+        <v>3.765320029869263</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.354991060848251</v>
+        <v>-5.39082469796495</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.774015544705239</v>
+        <v>1.759682089858559</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2601434912562177</v>
+        <v>0.0618009244610247</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.072454488112018</v>
+        <v>3.953448948034902</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.379581305083435</v>
+        <v>-5.415414942200134</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.765150624763876</v>
+        <v>1.750817169917196</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2601434912562177</v>
+        <v>0.0618009244610247</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.073425665864728</v>
+        <v>3.954420125787612</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.328542929076915</v>
+        <v>-5.364376566193614</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.786408879546239</v>
+        <v>1.77207542469956</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2601434912562177</v>
+        <v>0.0618009244610247</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.074268570244484</v>
+        <v>3.955263030167368</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.287403634210284</v>
+        <v>-5.323237271326983</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.821902696367037</v>
+        <v>1.807569241520357</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3012827861228485</v>
+        <v>0.1029402193276555</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.117990246038607</v>
+        <v>3.998984705961491</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.176797494130682</v>
+        <v>-5.212631131247381</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.682329148522812</v>
+        <v>1.667995693676133</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4118889262024505</v>
+        <v>0.2135463594072575</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.000537926210303</v>
+        <v>3.881532386133187</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.307378228661524</v>
+        <v>-5.343211865778223</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.633598898784439</v>
+        <v>1.619265443937759</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.281308191671608</v>
+        <v>0.08296562487641501</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.925691529565762</v>
+        <v>3.806685989488645</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.142881894470563</v>
+        <v>-5.178715531587262</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.683824251536906</v>
+        <v>1.669490796690227</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.281308191671608</v>
+        <v>0.08296562487641501</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.910118348641844</v>
+        <v>3.791112808564728</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.170251827154995</v>
+        <v>-5.206085464271694</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.672063988899563</v>
+        <v>1.657730534052884</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.281308191671608</v>
+        <v>0.08296562487641501</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.909306059078273</v>
+        <v>3.790300519001157</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.180637022044884</v>
+        <v>-5.216470659161583</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.67777869006868</v>
+        <v>1.663445235222</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2709229967817187</v>
+        <v>0.0725804299865257</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.912943721269412</v>
+        <v>3.793938181192297</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.199225180767109</v>
+        <v>-5.235058817883808</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.741180432356215</v>
+        <v>1.726846977509535</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2523348380594934</v>
+        <v>0.05399227126430034</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.972627831812503</v>
+        <v>3.853622291735386</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.199523727463145</v>
+        <v>-5.235357364579844</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.737930024496099</v>
+        <v>1.723596569649419</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2523348380594934</v>
+        <v>0.05399227126430034</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.969496842630801</v>
+        <v>3.850491302553685</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.098700593772717</v>
+        <v>-5.134534230889416</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.782790172911662</v>
+        <v>1.768456718064982</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2647990535438472</v>
+        <v>0.06645648674865418</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.981506266860804</v>
+        <v>3.862500726783689</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.90791923302031</v>
+        <v>-4.943752870137009</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.859231970691168</v>
+        <v>1.844898515844488</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4555804142962546</v>
+        <v>0.2572378475010615</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.096104336790792</v>
+        <v>3.977098796713676</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.88940237897849</v>
+        <v>-4.925236016095189</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.846475558045492</v>
+        <v>1.832142103198813</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4685105437214628</v>
+        <v>0.2701679769262698</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.083699260183513</v>
+        <v>3.964693720106398</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.864209194477172</v>
+        <v>-4.900042831593871</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.891519768458078</v>
+        <v>1.877186313611398</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4937037282227812</v>
+        <v>0.2953611614275881</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.133782107496363</v>
+        <v>4.014776567419247</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.852155067564209</v>
+        <v>-4.887988704680908</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.890027987124701</v>
+        <v>1.875694532278021</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.505757855135744</v>
+        <v>0.3074152883405509</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.134701151545578</v>
+        <v>4.015695611468463</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.858778314254567</v>
+        <v>-4.894611951371266</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.889259318632694</v>
+        <v>1.874925863786014</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4991346084453856</v>
+        <v>0.3007920416501926</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.132607833715499</v>
+        <v>4.013602293638384</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.755897724725974</v>
+        <v>-4.791731361842674</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.943262580322013</v>
+        <v>1.928929125475333</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6020151979739785</v>
+        <v>0.4036726311787855</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.207187213310537</v>
+        <v>4.088181673233422</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.779339763906061</v>
+        <v>-4.81517340102276</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.954088434823572</v>
+        <v>1.939754979976893</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6020151979739785</v>
+        <v>0.4036726311787855</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.227389883484132</v>
+        <v>4.108384343407016</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.797412272197673</v>
+        <v>-4.833245909314372</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.946859431506928</v>
+        <v>1.932525976660248</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6020151979739785</v>
+        <v>0.4036726311787855</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.227389883484132</v>
+        <v>4.108384343407016</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.028586066074305</v>
+        <v>-5.064419703191004</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.814641827549742</v>
+        <v>1.800308372703062</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6020151979739785</v>
+        <v>0.4036726311787855</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.187641797077599</v>
+        <v>4.068636257000483</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.99730004553385</v>
+        <v>-5.033133682650549</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.834178854762864</v>
+        <v>1.819845399916184</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6333012185144339</v>
+        <v>0.4349586517192409</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.213436028398812</v>
+        <v>4.094430488321696</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.844274653420565</v>
+        <v>-4.880108290537264</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.994560011181082</v>
+        <v>1.980226556334402</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.786326610627718</v>
+        <v>0.587984043832525</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.404422263239686</v>
+        <v>4.28541672316257</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.851411724605856</v>
+        <v>-4.887245361722555</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.179171407615258</v>
+        <v>2.164837952768578</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.786326610627718</v>
+        <v>0.587984043832525</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.591888488147979</v>
+        <v>4.472882948070863</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.423889058699156</v>
+        <v>3.668347396350242</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.988556275514219</v>
+        <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.851411724605856</v>
+        <v>-4.75827766603951</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.179171407615258</v>
+        <v>2.185827982395878</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.786326610627718</v>
+        <v>0.7169517395155697</v>
       </c>
       <c r="G2053" t="n">
-        <v>3.981620072500587</v>
+        <v>4.519666516834771</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240811.xlsx
+++ b/tame_output/ON/bt/strategyON_20240811.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>49.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.5%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.9%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-617.1%</t>
+          <t>-597.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.9%</t>
+          <t>430.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-637.4%</t>
+          <t>-636.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-247.2%</t>
+          <t>-239.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.6%</t>
+          <t>-157.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-248.6%</t>
+          <t>-228.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.3%</t>
+          <t>-296.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.3%</t>
+          <t>-147.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-149.5%</t>
+          <t>-137.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.459224753477259</v>
+        <v>-1.260882186682066</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.532873941737214</v>
+        <v>2.612210968455291</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.05553076382465</v>
+        <v>1.253873330619843</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.750238725736655</v>
+        <v>3.86924426581377</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911636</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.825293480621912</v>
+        <v>-1.626950913826719</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.379530750185801</v>
+        <v>2.458867776903879</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.6894620366799974</v>
+        <v>0.88780460347519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.523681788756312</v>
+        <v>3.642687328833428</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.033784262073596</v>
+        <v>-1.835441695278403</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.316472727343896</v>
+        <v>2.395809754061973</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.480971255228313</v>
+        <v>0.6793138220235055</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.41892560962407</v>
+        <v>3.537931149701186</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.280985446838818</v>
+        <v>-2.082642880043625</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.225691003846376</v>
+        <v>2.305028030564453</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.5011246087271254</v>
+        <v>0.699467175522318</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.439116372131926</v>
+        <v>3.558121912209042</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382324</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.773370474862915</v>
+        <v>-2.575027908067722</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.029843384680469</v>
+        <v>2.109180411398547</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.00873958070302866</v>
+        <v>0.2070821474982212</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.1447917473612</v>
+        <v>3.263797287438316</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.158550865792987</v>
+        <v>-2.960208298997795</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.874313767121304</v>
+        <v>1.953650793839381</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.00873958070302866</v>
+        <v>0.2070821474982212</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.143334286174063</v>
+        <v>3.262339826251179</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.29913614634705</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.408421545807569</v>
+        <v>-3.210078979012376</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.776134618570087</v>
+        <v>1.855471645288164</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.04500230053349191</v>
+        <v>0.2433448673286845</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.166861041526957</v>
+        <v>3.285866581604073</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130012</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.61493332269459</v>
+        <v>-3.416590755899398</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.689635966471537</v>
+        <v>1.768972993189614</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.1615094763535296</v>
+        <v>0.036833090441663</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.039060034051003</v>
+        <v>3.158065574128118</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.315884374178238</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.934277397775091</v>
+        <v>-3.735934830979899</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.563671263139596</v>
+        <v>1.643008289857673</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.1615094763535296</v>
+        <v>0.036833090441663</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.040832960751262</v>
+        <v>3.159838500828378</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.320487229050866</v>
+        <v>-4.122144662255674</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.39552021809669</v>
+        <v>1.474857244814767</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.2522824160709729</v>
+        <v>-0.05393984927578033</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.9727020843882</v>
+        <v>3.091707624465316</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.555181223183419</v>
+        <v>-4.356838656388226</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.28992739544576</v>
+        <v>1.369264422163837</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.2459461488417177</v>
+        <v>-0.04760358204652515</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.964788619727844</v>
+        <v>3.08379415980496</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.890843870413871</v>
+        <v>-4.692501303618679</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.154242928209544</v>
+        <v>1.233579954927621</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.3138771343306225</v>
+        <v>-0.11553456753543</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.922610620090466</v>
+        <v>3.041616160167582</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.967288200616743</v>
+        <v>-4.76894563382155</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.130152756362637</v>
+        <v>1.209489783080714</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.2334316252369606</v>
+        <v>-0.03508905844176807</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.977365485780905</v>
+        <v>3.096371025858021</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.332415583255489</v>
+        <v>-5.134073016460297</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9833563183129694</v>
+        <v>1.062693345031047</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.5297424095359732</v>
+        <v>-0.3313998427407806</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.798833530207329</v>
+        <v>2.917839070284444</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.741004360436168</v>
+        <v>-5.542661793640976</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8186823514554571</v>
+        <v>0.8980193781735339</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.9383311867166516</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.552441807913681</v>
+        <v>2.671447347990797</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.854764772459033</v>
+        <v>-5.656422205663841</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7683636191177716</v>
+        <v>0.8477006458358489</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.9383311867166516</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.547627240385141</v>
+        <v>2.666632780462257</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.27115664674603</v>
+        <v>-6.072814079950838</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5998009200118499</v>
+        <v>0.6791379467299272</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.9383311867166516</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.545621290994019</v>
+        <v>2.664626831071135</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.632330276563018</v>
+        <v>-6.433987709767826</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4655901587537339</v>
+        <v>0.5449271854718107</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.9383311867166516</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.555879981662698</v>
+        <v>2.674885521739814</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.975588796206037</v>
+        <v>-6.777246229410845</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3243863160422218</v>
+        <v>0.4037233427602986</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.9383311867166516</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.551979546808393</v>
+        <v>2.670985086885509</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.023791613448381</v>
+        <v>-6.825449046653189</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.303510109200285</v>
+        <v>0.3828471359183618</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.9383311867166516</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.550384466863394</v>
+        <v>2.669390006940509</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.320452955258578</v>
+        <v>-7.122110388463386</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1886245484054143</v>
+        <v>0.2679615751234912</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.00707432245053</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.512917561352275</v>
+        <v>2.631923101429391</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.507172663567881</v>
+        <v>-7.308830096772689</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.10991036054729</v>
+        <v>0.1892473872653668</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.00707432245053</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.508891256817872</v>
+        <v>2.627896796894988</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.890174052310512</v>
+        <v>-7.69183148551532</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.04339229627134644</v>
+        <v>0.03594473044673041</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.00707432245053</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.508789155496288</v>
+        <v>2.627794695573404</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.894660497511901</v>
+        <v>-7.696317930716709</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.04261535838047203</v>
+        <v>0.03672166833760526</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.011560767651919</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.508668804346885</v>
+        <v>2.627674344424</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.254190820015904</v>
+        <v>-8.055848253220711</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1810771840840228</v>
+        <v>-0.1017401573659455</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.011560767651919</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.514019107644935</v>
+        <v>2.63302464772205</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.304539883470126</v>
+        <v>-8.106197316674933</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1933007895085339</v>
+        <v>-0.1139637627904571</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.061909831106141</v>
+        <v>-0.8635672643109484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.491725689529579</v>
+        <v>2.610731229606695</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.402159160891522</v>
+        <v>-8.203816594096329</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2293067498553234</v>
+        <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.159529108527537</v>
+        <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.43619587369851</v>
+        <v>2.555201413775626</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.45623066039988</v>
+        <v>-8.257888093604688</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2480417933370949</v>
+        <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.213600608035897</v>
+        <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.406646530315067</v>
+        <v>2.525652070392182</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.660488835729744</v>
+        <v>-8.462146268934552</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3242318663503978</v>
+        <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.341239552649886</v>
+        <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.335576360665315</v>
+        <v>2.454581900742431</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.694141674238217</v>
+        <v>-8.495799107443025</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3332104472693511</v>
+        <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.441652920566923</v>
+        <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.279810894399529</v>
+        <v>2.398816434476645</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.620671842570768</v>
+        <v>-8.422329275775576</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2884508131089505</v>
+        <v>-0.2091137863908736</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.368183088899475</v>
+        <v>-1.169840522104282</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.33926449489342</v>
+        <v>2.458270034970535</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.795796259957312</v>
+        <v>-8.597453693162119</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3439453593160513</v>
+        <v>-0.264608332597974</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.543307506286019</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.24874506520901</v>
+        <v>2.367750605286126</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.030248353971801</v>
+        <v>-8.831905787176609</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4449453618234429</v>
+        <v>-0.3656083351053661</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.543307506286019</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.241525900307414</v>
+        <v>2.36053144038453</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.134623084998248</v>
+        <v>-8.936280518203056</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4933674450079977</v>
+        <v>-0.4140304182899208</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.647682237312464</v>
+        <v>-1.449339670517272</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.172228870917571</v>
+        <v>2.291234410994686</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.297136550696832</v>
+        <v>-9.09879398390164</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5572570414488753</v>
+        <v>-0.477920014730798</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.745315667731151</v>
+        <v>-1.546973100935959</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.114764602504914</v>
+        <v>2.23377014258203</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.423173344065122</v>
+        <v>-9.224830777269929</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6049780301670764</v>
+        <v>-0.5256410034489991</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.720064044921409</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.132609304819875</v>
+        <v>2.25161484489699</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.366101572169191</v>
+        <v>-9.167759005373998</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5781589857223031</v>
+        <v>-0.4988219590042262</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.720064044921409</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.136599640506275</v>
+        <v>2.255605180583391</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.507773413893311</v>
+        <v>-9.309430847098119</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6363029493106929</v>
+        <v>-0.556965922592616</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.720064044921409</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.135124413607534</v>
+        <v>2.254129953684649</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.458182569468477</v>
+        <v>-9.259840002673284</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6014132013758871</v>
+        <v>-0.5220761746578098</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.670473200496575</v>
+        <v>-1.472130633701382</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.179932330427306</v>
+        <v>2.298937870504422</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.30926423499662</v>
+        <v>-9.110921668201428</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5548970012338272</v>
+        <v>-0.4755599745157504</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.639223609761402</v>
+        <v>-1.440881042966209</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.185630951221727</v>
+        <v>2.304636491298843</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.08341908227721</v>
+        <v>-8.885076515482016</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4549798671098544</v>
+        <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.597296934174238</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.220366029610234</v>
+        <v>2.33937156968735</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.958840425939618</v>
+        <v>-8.760497859144424</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4040092600187588</v>
+        <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.597296934174238</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.221505174166293</v>
+        <v>2.340510714243409</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.011735713983905</v>
+        <v>-8.813393147188711</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4225336010743659</v>
+        <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.592341588085792</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.227112155981468</v>
+        <v>2.346117696058584</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.939602538696024</v>
+        <v>-8.741259971900829</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3879466267205771</v>
+        <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.592341588085792</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.232845860220105</v>
+        <v>2.351851400297221</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.868236146086376</v>
+        <v>-8.669893579291182</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3691373320705833</v>
+        <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.520975195476144</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.265928433392029</v>
+        <v>2.384933973469144</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.774777112101152</v>
+        <v>-8.576434545305958</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.341637199789401</v>
+        <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.520975195476144</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.256044952079121</v>
+        <v>2.375050492156237</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.76412393054772</v>
+        <v>-8.565781363752526</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.339210487667402</v>
+        <v>-0.2598734609493243</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.520975195476144</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.254210391579747</v>
+        <v>2.373215931656863</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.66621689187123</v>
+        <v>-8.467874325076036</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3003479871702668</v>
+        <v>-0.221010960452189</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.452989445615588</v>
+        <v>-1.254646878820395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.29470152652262</v>
+        <v>2.413707066599736</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.642263350895272</v>
+        <v>-8.443920784100078</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2900980646343898</v>
+        <v>-0.2107610379163121</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.42903590463963</v>
+        <v>-1.230693337844438</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.309742157253688</v>
+        <v>2.428747697330804</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.378203412572475</v>
+        <v>-8.179860845777281</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1977344054670231</v>
+        <v>-0.1183973787489458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.164975966316834</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.454917804085614</v>
+        <v>2.57392334416273</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.671123789067637</v>
+        <v>-7.472781222272443</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.08231041027461128</v>
+        <v>0.1616474369926886</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.164975966316834</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.452130770425313</v>
+        <v>2.571136310502429</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.630939490701446</v>
+        <v>-7.432596923906252</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.09872775350892882</v>
+        <v>0.1780647802270061</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.124791667950643</v>
+        <v>-0.9264491011554506</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.476584973332869</v>
+        <v>2.595590513409984</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.467539619762084</v>
+        <v>-7.26919705296689</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1634545231054307</v>
+        <v>0.242791549823508</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9613917970112806</v>
+        <v>-0.7630492302160882</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.573991717117243</v>
+        <v>2.692997257194359</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.234058397532485</v>
+        <v>-7.035715830737291</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2647714408351223</v>
+        <v>0.3441084675532</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7279105747816821</v>
+        <v>-0.5295680079864896</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.722004879292855</v>
+        <v>2.841010419369971</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.08439200652497</v>
+        <v>-6.886049439729776</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3217457869251694</v>
+        <v>0.4010828136432467</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6350070835391461</v>
+        <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.774854763725417</v>
+        <v>2.893860303802533</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.952116532894084</v>
+        <v>-6.75377396609889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3700234631245509</v>
+        <v>0.4493604898426287</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5027316099082595</v>
+        <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.849587534650976</v>
+        <v>2.968593074728092</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.796378200334342</v>
+        <v>-6.598035633539148</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4351338568360843</v>
+        <v>0.514470883554162</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3469932773485179</v>
+        <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.945845594874458</v>
+        <v>3.064851134951573</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.711413533605022</v>
+        <v>-6.513070966809828</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4820260647514711</v>
+        <v>0.5613630914695489</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2620286106191984</v>
+        <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.009730736135708</v>
+        <v>3.128736276212824</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.817003523378126</v>
+        <v>-6.618660956582932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3118141392430105</v>
+        <v>0.3911511659610882</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3676186003923027</v>
+        <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.818400812672627</v>
+        <v>2.937406352749742</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.835738425496723</v>
+        <v>-6.637395858701529</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3528645202726581</v>
+        <v>0.4322015469907359</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.373214610052434</v>
+        <v>-0.1748720432572415</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.863587548753634</v>
+        <v>2.98259308883075</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.687798384089124</v>
+        <v>-6.48945581729393</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2921616141475303</v>
+        <v>0.371498640865608</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3528936941438764</v>
+        <v>-0.154551127348684</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.755901175610601</v>
+        <v>2.874906715687717</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.634828861835135</v>
+        <v>-6.436486295039941</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3046354367956474</v>
+        <v>0.3839724635137252</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2999241718898876</v>
+        <v>-0.1015816050946951</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.778968902709517</v>
+        <v>2.897974442786632</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.469040665874845</v>
+        <v>-6.270698099079651</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3639901030846708</v>
+        <v>0.4433271298027481</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2999241718898876</v>
+        <v>-0.1015816050946951</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.772008290614424</v>
+        <v>2.891013830691539</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.435677459396076</v>
+        <v>-6.237334892600882</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3917977400573212</v>
+        <v>0.4711347667753989</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2999241718898876</v>
+        <v>-0.1015816050946951</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.786470644995567</v>
+        <v>2.905476185072682</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.327418322273554</v>
+        <v>-6.12907575547836</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4296335153655249</v>
+        <v>0.5089705420836026</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2999241718898876</v>
+        <v>-0.1015816050946951</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.781002765454762</v>
+        <v>2.900008305531877</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.204127187456423</v>
+        <v>-6.005784620661229</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.476448063302954</v>
+        <v>0.5557850900210317</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1766330370727571</v>
+        <v>0.02170952972243539</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.852475540355617</v>
+        <v>2.971481080432732</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.151430320325132</v>
+        <v>-5.953087753529938</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.505227788392796</v>
+        <v>0.5845648151108738</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1239361699414659</v>
+        <v>0.07440639685372658</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.891794638871717</v>
+        <v>3.010800178948832</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.907664878341688</v>
+        <v>-5.709322311546494</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5985146735332245</v>
+        <v>0.6778517002513018</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1239361699414659</v>
+        <v>0.07440639685372658</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.887575347218768</v>
+        <v>3.006580887295883</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.817889205965216</v>
+        <v>-5.619546639170022</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6365492564038293</v>
+        <v>0.7158862831219071</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.06233672502715587</v>
+        <v>0.1360058417680366</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.926659328087369</v>
+        <v>3.045664868164485</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.568038812016141</v>
+        <v>-5.369696245220947</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7292314889671614</v>
+        <v>0.8085685156852387</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.06233672502715587</v>
+        <v>0.1360058417680366</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.919401403071071</v>
+        <v>3.038406943148187</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.392146719548709</v>
+        <v>-5.193804152753515</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8031874494747826</v>
+        <v>0.8825244761928603</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.06233672502715587</v>
+        <v>0.1360058417680366</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.92300052659172</v>
+        <v>3.042006066668836</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.220700256526245</v>
+        <v>-5.022357689731051</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.885093540738322</v>
+        <v>0.9644305674563993</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1091097379953073</v>
+        <v>0.3074523047904997</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.039195910459752</v>
+        <v>3.158201450536867</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.146410690787906</v>
+        <v>-4.948068123992712</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9138298446499546</v>
+        <v>0.9931668713680322</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1833993037336465</v>
+        <v>0.381741870528839</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.082790127519052</v>
+        <v>3.201795667596168</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.082774948553972</v>
+        <v>-4.884432381758778</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9439789425978455</v>
+        <v>1.023315969315923</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2470350459675811</v>
+        <v>0.4453776127627735</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.12566637391373</v>
+        <v>3.244671913990846</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.971348189228052</v>
+        <v>-4.773005622432858</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9697439051120091</v>
+        <v>1.049080931830087</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2470350459675811</v>
+        <v>0.4453776127627735</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.106860632697526</v>
+        <v>3.225866172774642</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.981850812293341</v>
+        <v>-4.783508245498147</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.967285932510771</v>
+        <v>1.046622959228849</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2365324229022922</v>
+        <v>0.4348749896974847</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.10230213548323</v>
+        <v>3.221307675560346</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.909608244122146</v>
+        <v>-4.711265677326952</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.000112273614069</v>
+        <v>1.079449300332147</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2365324229022922</v>
+        <v>0.4348749896974847</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.10623144931805</v>
+        <v>3.225236989395166</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.891894557244281</v>
+        <v>-4.693551990449087</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.007876332282555</v>
+        <v>1.087213359000633</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.239713751799209</v>
+        <v>0.4380563185944015</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10881883057354</v>
+        <v>3.227824370650656</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.783089671764554</v>
+        <v>-4.58474710496936</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.04839635769444</v>
+        <v>1.127733384412517</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.239713751799209</v>
+        <v>0.4380563185944015</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.105816901793534</v>
+        <v>3.224822441870649</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.563068873727543</v>
+        <v>-4.364726306932349</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.137983713919858</v>
+        <v>1.217320740637936</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3809335968671893</v>
+        <v>0.5792761636623818</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.192127845844936</v>
+        <v>3.311133385922052</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.430201184664265</v>
+        <v>-4.231858617869071</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.207024972346992</v>
+        <v>1.28636199906507</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3809335968671893</v>
+        <v>0.5792761636623818</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.208022028646759</v>
+        <v>3.327027568723875</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.310028101299767</v>
+        <v>-4.111685534504573</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.256240050133094</v>
+        <v>1.335577076851171</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5011066802316881</v>
+        <v>0.6994492470268807</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.28127172310576</v>
+        <v>3.400277263182876</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.17477473996979</v>
+        <v>-3.976432173174596</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.320429497226524</v>
+        <v>1.399766523944602</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6363600415616653</v>
+        <v>0.8347026083568578</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.372511842465187</v>
+        <v>3.491517382542302</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.234649567327482</v>
+        <v>-4.036307000532288</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.282517057684873</v>
+        <v>1.361854084402951</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5764852142039731</v>
+        <v>0.7748277809991657</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.322624437451998</v>
+        <v>3.441629977529113</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.114829336416645</v>
+        <v>-3.91648676962145</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.345734319283417</v>
+        <v>1.425071346001494</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5764852142039731</v>
+        <v>0.7748277809991657</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.337913606686206</v>
+        <v>3.456919146763322</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.117299042878451</v>
+        <v>-3.918956476083256</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.252390636021136</v>
+        <v>1.331727662739214</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5740155077421669</v>
+        <v>0.7723580745373595</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.244075982131564</v>
+        <v>3.363081522208679</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.185669229202461</v>
+        <v>-3.987326662407266</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.144304422976833</v>
+        <v>1.223641449694911</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5832912067783819</v>
+        <v>0.7816337735735744</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.168903263038594</v>
+        <v>3.28790880311571</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.199457282049508</v>
+        <v>-4.001114715254313</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.129225910469906</v>
+        <v>1.208562937187984</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5832912067783819</v>
+        <v>0.7816337735735744</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.159339971670486</v>
+        <v>3.278345511747601</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.254977357942098</v>
+        <v>-4.056634791146903</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.244048716805072</v>
+        <v>1.32338574352315</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5832912067783819</v>
+        <v>0.7816337735735744</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.296370808362687</v>
+        <v>3.415376348439803</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.079503098149628</v>
+        <v>-3.881160531354433</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.318805652713848</v>
+        <v>1.398142679431926</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5832912067783819</v>
+        <v>0.7816337735735744</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.300938040354476</v>
+        <v>3.419943580431591</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.190439350790877</v>
+        <v>-3.992096783995682</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.250173180418555</v>
+        <v>1.329510207136633</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5832912067783819</v>
+        <v>0.7816337735735744</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.276680069115683</v>
+        <v>3.395685609192798</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.156775805318595</v>
+        <v>-3.9584332385234</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.192176912008918</v>
+        <v>1.271513938726996</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6169547522506638</v>
+        <v>0.8152973190458563</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.225416509800501</v>
+        <v>3.344422049877617</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.096923186114871</v>
+        <v>-3.898580619319677</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.22629034612254</v>
+        <v>1.305627372840617</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6169547522506638</v>
+        <v>0.8152973190458563</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.235588896232634</v>
+        <v>3.35459443630975</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.010679723088494</v>
+        <v>-3.8123371562933</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.255734001906951</v>
+        <v>1.335071028625029</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6169547522506638</v>
+        <v>0.8152973190458563</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.230535166806494</v>
+        <v>3.34954070688361</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.055986542487473</v>
+        <v>-3.857643975692279</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.229387049591885</v>
+        <v>1.308724076309962</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.576144589241433</v>
+        <v>0.7744871560366255</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.197824844445481</v>
+        <v>3.316830384522597</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803195</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.085019647189775</v>
+        <v>-3.886677080394581</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.218325680744066</v>
+        <v>1.297662707462143</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.576144589241433</v>
+        <v>0.7744871560366255</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.198376717478583</v>
+        <v>3.317382257555698</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.992209165738915</v>
+        <v>-3.793866598943722</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.184722565215775</v>
+        <v>1.264059591933853</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6689550706922923</v>
+        <v>0.8672976374874849</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.183335698240464</v>
+        <v>3.30234123831758</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.036598635068343</v>
+        <v>-3.838256068273149</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.168840253408605</v>
+        <v>1.248177280126682</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6245656013628647</v>
+        <v>0.8229081681580572</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.158575492567408</v>
+        <v>3.277581032644524</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.153140240173686</v>
+        <v>-3.954797673378492</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.117299319878191</v>
+        <v>1.196636346596268</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5080239962575219</v>
+        <v>0.7063665630527145</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.083726238015926</v>
+        <v>3.202731778093042</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798541</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.193064334756258</v>
+        <v>-3.994721767961064</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.106820977875829</v>
+        <v>1.186158004593907</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5080239962575219</v>
+        <v>0.7063665630527145</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.089217533846593</v>
+        <v>3.208223073923708</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.220844732657611</v>
+        <v>-4.022502165862416</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.107206020483827</v>
+        <v>1.186543047201905</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4802435983561689</v>
+        <v>0.6785861651513614</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.08404649687432</v>
+        <v>3.203052036951436</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.339225405387749</v>
+        <v>-4.140882838592555</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8982094713924251</v>
+        <v>0.9775464981105026</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4130257462051927</v>
+        <v>0.6113683130003852</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.882071505584388</v>
+        <v>3.001077045661503</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.44783948383108</v>
+        <v>-4.249496917035886</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9749135007342982</v>
+        <v>1.054250527452376</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4130257462051927</v>
+        <v>0.6113683130003852</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.002221166303593</v>
+        <v>3.121226706380709</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.412430445582937</v>
+        <v>-4.214087878787743</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.003590142135878</v>
+        <v>1.082927168853956</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4130257462051927</v>
+        <v>0.6113683130003852</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.016734192405916</v>
+        <v>3.135739732483032</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913429</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.374046783024786</v>
+        <v>-4.175704216229592</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.016363048501507</v>
+        <v>1.095700075219585</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4514094087633438</v>
+        <v>0.6497519755585364</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.037183831283176</v>
+        <v>3.156189371360291</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.19693045298962</v>
+        <v>-3.998587886194426</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.083938609360876</v>
+        <v>1.163275636078954</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4514094087633438</v>
+        <v>0.6497519755585364</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.033912860128478</v>
+        <v>3.152918400205593</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793907</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.242022697823166</v>
+        <v>-4.043680131027972</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.066585103189371</v>
+        <v>1.145922129907448</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3895133655939541</v>
+        <v>0.5878559323891466</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.997458625988757</v>
+        <v>3.116464166065872</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.062647276584398</v>
+        <v>-3.864304709789204</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.132122246991292</v>
+        <v>1.21145927370937</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5462901237646727</v>
+        <v>0.7446326905598653</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.085311656197602</v>
+        <v>3.204317196274718</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982232</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.107661490105004</v>
+        <v>-3.90931892330981</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.094924016914639</v>
+        <v>1.174261043632717</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5159412284500681</v>
+        <v>0.7142837952452606</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.047909774340429</v>
+        <v>3.166915314417545</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.374666000377439</v>
+        <v>-4.176323433582246</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9938137751446112</v>
+        <v>1.073150801862689</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3215781904071195</v>
+        <v>0.5199207572023121</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.936983513853606</v>
+        <v>3.055989053930722</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.475863781814612</v>
+        <v>-4.277521215019418</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9525385844662435</v>
+        <v>1.031875611184321</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2531693768618003</v>
+        <v>0.4515119436569929</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.895142147622916</v>
+        <v>3.014147687700031</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.469352815200299</v>
+        <v>-4.271010248405106</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9527429326662853</v>
+        <v>1.032079959384363</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2531693768618003</v>
+        <v>0.4515119436569929</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.892742109177233</v>
+        <v>3.011747649254348</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.450314687493002</v>
+        <v>-4.251972120697808</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9568829029574493</v>
+        <v>1.036219929675527</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1949857655306058</v>
+        <v>0.3933283323257984</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.854356661586761</v>
+        <v>2.973362201663877</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.502830489767822</v>
+        <v>-4.304487922972629</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.055170983681711</v>
+        <v>1.134508010399789</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1949857655306058</v>
+        <v>0.3933283323257984</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.973651063220951</v>
+        <v>3.092656603298067</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.51669725110174</v>
+        <v>-4.318354684306547</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.050457608134278</v>
+        <v>1.129794634852355</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1571278487967828</v>
+        <v>0.3554704155919755</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.951769642166791</v>
+        <v>3.070775182243906</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.47189307956181</v>
+        <v>-4.273550512766617</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.074387807147176</v>
+        <v>1.153724833865253</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1571278487967828</v>
+        <v>0.3554704155919755</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.957778172563717</v>
+        <v>3.076783712640832</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.324150109326808</v>
+        <v>-4.125807542531614</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.031435216518376</v>
+        <v>1.110772243236454</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.324935206031666</v>
+        <v>0.5232777728268586</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.956412808181846</v>
+        <v>3.075418348258962</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.407971330601506</v>
+        <v>-4.209628763806313</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.000700349539978</v>
+        <v>1.080037376258055</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.324935206031666</v>
+        <v>0.5232777728268586</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.959206429713327</v>
+        <v>3.078211969790443</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.401818624548722</v>
+        <v>-4.203476057753528</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.00382378035275</v>
+        <v>1.083160807070827</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3310879120844503</v>
+        <v>0.5294304788796429</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.963560401736656</v>
+        <v>3.082565941813772</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.418627922699224</v>
+        <v>-4.22028535590403</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9961805378326594</v>
+        <v>1.075517564550737</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3142786139339486</v>
+        <v>0.5126211807291412</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.952555299586465</v>
+        <v>3.071560839663581</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.356329923923101</v>
+        <v>-4.157987357127908</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.087435291139929</v>
+        <v>1.166772317858007</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3595728782083907</v>
+        <v>0.5579154450035833</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.046067411947952</v>
+        <v>3.165072952025067</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.154539726257943</v>
+        <v>-3.95619715946275</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9704433719201195</v>
+        <v>1.049780398638197</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5575910703775451</v>
+        <v>0.7559336371727376</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.967170328963571</v>
+        <v>3.086175869040687</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.205426438944138</v>
+        <v>-4.007083872148945</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.020378919167817</v>
+        <v>1.099715945885894</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5067043576913506</v>
+        <v>0.7050469244865432</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.00692853367403</v>
+        <v>3.125934073751146</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.118815696294331</v>
+        <v>-3.920473129499138</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.069650952343783</v>
+        <v>1.148987979061861</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5853300888965088</v>
+        <v>0.7836726556917014</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.068731708513168</v>
+        <v>3.187737248590284</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.179024994299616</v>
+        <v>-3.980682427504422</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.044103213966341</v>
+        <v>1.123440240684419</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5251207908912243</v>
+        <v>0.7234633576864169</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.031142110534669</v>
+        <v>3.150147650611785</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397797</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.102602947867689</v>
+        <v>-3.904260381072495</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.07316365057904</v>
+        <v>1.152500677297118</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5251207908912243</v>
+        <v>0.7234633576864169</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.029633728574598</v>
+        <v>3.148639268651714</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.058229816229121</v>
+        <v>-3.859887249433926</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.090775770669904</v>
+        <v>1.170112797387981</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5694939225297929</v>
+        <v>0.7678364893249855</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.056120474993175</v>
+        <v>3.175126015070291</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.080710167088005</v>
+        <v>-3.882367600292811</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.07617742446494</v>
+        <v>1.155514451183018</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5694939225297929</v>
+        <v>0.7678364893249855</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.050514269131765</v>
+        <v>3.169519809208881</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.03305443652695</v>
+        <v>-3.834711869731755</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.101621473717167</v>
+        <v>1.180958500435245</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6171496530908486</v>
+        <v>0.8154922198860411</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.085489464496204</v>
+        <v>3.20449500457332</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.932536278028195</v>
+        <v>-3.734193711233001</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.146721110491394</v>
+        <v>1.226058137209472</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7176678115896031</v>
+        <v>0.9160103783847957</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.150692732970181</v>
+        <v>3.269698273047297</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.916630948595842</v>
+        <v>-3.718288381800648</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.139837914740207</v>
+        <v>1.219174941458285</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6385551508803642</v>
+        <v>0.8368977176755568</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.08997980902051</v>
+        <v>3.208985349097626</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932772</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.871792546987444</v>
+        <v>-3.67344998019225</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.161870977994195</v>
+        <v>1.241208004712273</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6430985838252337</v>
+        <v>0.8414411506204262</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.09680357139806</v>
+        <v>3.215809111475176</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917055</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.891291003229453</v>
+        <v>-3.692948436434258</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.15823253512847</v>
+        <v>1.237569561846547</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5950139425453294</v>
+        <v>0.7933565093405219</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.072113726261196</v>
+        <v>3.191119266338311</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405962</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.847088166143552</v>
+        <v>-3.648745599348358</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.181793272490667</v>
+        <v>1.261130299208745</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6392167796312298</v>
+        <v>0.8375593464264224</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.104515031040573</v>
+        <v>3.223520571117689</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265647</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.884067193806995</v>
+        <v>-3.638141534693455</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.165411661894537</v>
+        <v>1.263781925539954</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6761906814225603</v>
+        <v>0.8971167260099515</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.125109372584619</v>
+        <v>3.257664999337054</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284882</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.725775776267723</v>
+        <v>-3.479850117154183</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.279975994093286</v>
+        <v>1.378346257738702</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6761906814225603</v>
+        <v>0.8971167260099515</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.176357137767659</v>
+        <v>3.308912764520094</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321026</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.518133772633247</v>
+        <v>-3.272208113519707</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.36147350014133</v>
+        <v>1.459843763786746</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8838326850570365</v>
+        <v>1.104758729644428</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.299383044542598</v>
+        <v>3.431938671295033</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475143</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.467101679910719</v>
+        <v>-3.221176020797178</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.376834565468611</v>
+        <v>1.475204829114027</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9348647777795644</v>
+        <v>1.155790822366956</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.324950528414385</v>
+        <v>3.457506155166819</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404858</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.401877498783513</v>
+        <v>-3.155951839669973</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.420111642012198</v>
+        <v>1.518481905657614</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.00008895890677</v>
+        <v>1.221015003494161</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.381272441183413</v>
+        <v>3.513828067935847</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882561</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.364450478712379</v>
+        <v>-3.118524819598839</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.431043422339932</v>
+        <v>1.529413685985348</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.005340496935952</v>
+        <v>1.226266541523343</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.380384336300202</v>
+        <v>3.512939963052637</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992664</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.384562134747088</v>
+        <v>-3.138636475633547</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.424255552257289</v>
+        <v>1.522625815902705</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.016367841933371</v>
+        <v>1.237293886520762</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.388257535629894</v>
+        <v>3.520813162382329</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636291</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.330817320319883</v>
+        <v>-3.084891661206342</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.606311249049382</v>
+        <v>1.704681512694798</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.026431151373833</v>
+        <v>1.247357195961224</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.554853292315382</v>
+        <v>3.687408919067817</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095763</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.25603505929487</v>
+        <v>-3.01010940018133</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.756337062677204</v>
+        <v>1.85470732632262</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.101213412398846</v>
+        <v>1.322139456986237</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.719835558148207</v>
+        <v>3.852391184900641</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998759</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.229950975031062</v>
+        <v>-2.984025315917522</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.758478672396586</v>
+        <v>1.856848936042002</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.101213412398846</v>
+        <v>1.322139456986237</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.711543534162066</v>
+        <v>3.8440991609145</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896933</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.142073061921942</v>
+        <v>-2.896147402808401</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.791823033224014</v>
+        <v>1.89019329686943</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.217139054822197</v>
+        <v>1.438065099409588</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.779292115199856</v>
+        <v>3.911847741952291</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959861</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.133180600528658</v>
+        <v>-2.887254941415118</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.812934423508118</v>
+        <v>1.911304687153535</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.217139054822197</v>
+        <v>1.438065099409588</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.796846520926647</v>
+        <v>3.929402147679082</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945368</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.301656717498536</v>
+        <v>-3.055731058384996</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.737399024124751</v>
+        <v>1.835769287770167</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.189191219105616</v>
+        <v>1.410117263693007</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.771932866901283</v>
+        <v>3.904488493653718</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782711</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.603857188636953</v>
+        <v>-2.357931529523412</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.997788532857246</v>
+        <v>2.096158796502662</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.118843159735205</v>
+        <v>1.339769204322597</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.710993728466898</v>
+        <v>3.843549355219333</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563264</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.5811360849538</v>
+        <v>-2.33521042584026</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.997540996827412</v>
+        <v>2.095911260472828</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.118843159735205</v>
+        <v>1.339769204322597</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.701657750963803</v>
+        <v>3.834213377716237</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777677</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.710337898247843</v>
+        <v>-2.464412239134302</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.104766397360964</v>
+        <v>2.20313666100638</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9896413464411631</v>
+        <v>1.210567391028554</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.783042788838546</v>
+        <v>3.915598415590981</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644416</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.865118905026098</v>
+        <v>-2.619193245912558</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.079931817143308</v>
+        <v>2.178302080788725</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9562736723866869</v>
+        <v>1.177199716974078</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.800100006899507</v>
+        <v>3.932655633651942</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799968</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.858064214810925</v>
+        <v>-2.612138555697384</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.079429049218923</v>
+        <v>2.177799312864339</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9633283626018607</v>
+        <v>1.184254407189252</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.801008177018157</v>
+        <v>3.933563803770592</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331119</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.831112990484437</v>
+        <v>-2.585187331370896</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.10021569259426</v>
+        <v>2.198585956239676</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9782087086295799</v>
+        <v>1.199134753216971</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.81994253827953</v>
+        <v>3.952498165031964</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784112</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.967065998540753</v>
+        <v>-2.721140339427213</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.229937621516693</v>
+        <v>2.328307885162109</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9782087086295799</v>
+        <v>1.199134753216971</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.00404567042449</v>
+        <v>4.136601297176925</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.989474116345625</v>
+        <v>-2.743548457232085</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.213091069297737</v>
+        <v>2.311461332943153</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9782087086295799</v>
+        <v>1.199134753216971</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.996162365327483</v>
+        <v>4.128717992079918</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155036</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.017698351923225</v>
+        <v>-2.771772692809685</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.203855374616334</v>
+        <v>2.302225638261751</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9961854610808885</v>
+        <v>1.21711150566828</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.009002416347905</v>
+        <v>4.14155804310034</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.027139277811755</v>
+        <v>-2.781213618698215</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.25633272198277</v>
+        <v>2.354702985628186</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.11861257862428</v>
+        <v>1.339538623211671</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.138712404595787</v>
+        <v>4.271268031348222</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321638</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.079412885147397</v>
+        <v>-2.833487226033856</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.238314373593814</v>
+        <v>2.33668463723923</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.066338971288639</v>
+        <v>1.28726501587603</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.110239334739703</v>
+        <v>4.242794961492138</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.155742862748303</v>
+        <v>-2.909817203634762</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.205894195447227</v>
+        <v>2.304264459092643</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.066338971288639</v>
+        <v>1.28726501587603</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.108351147633479</v>
+        <v>4.240906774385913</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.357996583072656</v>
+        <v>-3.112070923959116</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.119812936920348</v>
+        <v>2.218183200565764</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8640852509642851</v>
+        <v>1.085011295551676</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.981819145041729</v>
+        <v>4.114374771794163</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.71289761234307</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.519565008599911</v>
+        <v>-3.273639349486371</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.053619576919598</v>
+        <v>2.151989840565014</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7373023271664058</v>
+        <v>0.958228371753797</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.904183400973154</v>
+        <v>4.036739027725588</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389353</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.651866300697464</v>
+        <v>-3.405940641583924</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.013772466946495</v>
+        <v>2.112142730591912</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7373023271664058</v>
+        <v>0.958228371753797</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.917256807839072</v>
+        <v>4.049812434591507</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378396</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.837734611536694</v>
+        <v>-3.591808952423154</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.931430339393743</v>
+        <v>2.02980060303916</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5787367338464581</v>
+        <v>0.7996627784338494</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.814122648630043</v>
+        <v>3.946678275382478</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006979</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.865635398646167</v>
+        <v>-3.619709739532627</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.918794065676956</v>
+        <v>2.017164329322372</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5441398097035233</v>
+        <v>0.7650658542909146</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.791888535271284</v>
+        <v>3.924444162023719</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.988161501349061</v>
+        <v>-3.742235842235521</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.866548068572997</v>
+        <v>1.964918332218414</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4216137070006294</v>
+        <v>0.6425397515880207</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.715137317626747</v>
+        <v>3.847692944379182</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585941</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.21867599753465</v>
+        <v>-3.972750338421109</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.841048229689266</v>
+        <v>1.939418493334682</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1910992108150407</v>
+        <v>0.412025255402432</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.643534579505897</v>
+        <v>3.776090206258332</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814668</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.475396815529473</v>
+        <v>-4.229471156415933</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.878671621493183</v>
+        <v>1.9770418851386</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.08268463667122583</v>
+        <v>0.3036106812586171</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.718797554021456</v>
+        <v>3.851353180773891</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.629383233305614</v>
+        <v>-4.403896638549326</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.886057323528367</v>
+        <v>1.976251961430882</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.08268463667122583</v>
+        <v>0.3036106812586171</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.787777823167096</v>
+        <v>3.92033344991953</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.578861329477948</v>
+        <v>-4.35337473472166</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.892317287179554</v>
+        <v>1.982511925082069</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.08268463667122583</v>
+        <v>0.3036106812586171</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.773829025287216</v>
+        <v>3.906384652039651</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.831336483485672</v>
+        <v>-4.605849888729384</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.803197714631879</v>
+        <v>1.893392352534394</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.08268463667122583</v>
+        <v>0.3036106812586171</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.78569951434263</v>
+        <v>3.918255141095065</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67402853597316</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.124232239965084</v>
+        <v>-4.898745645208797</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.687249946559057</v>
+        <v>1.777444584461572</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.08268463667122583</v>
+        <v>0.3036106812586171</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.786910048861574</v>
+        <v>3.919465675614009</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251949</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.281776311694526</v>
+        <v>-5.056289716938238</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.628354060094602</v>
+        <v>1.718548697997117</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.01578283153095134</v>
+        <v>0.2367088761183426</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.75089070800473</v>
+        <v>3.883446334757166</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.5597407072778</v>
+        <v>-5.334254112521512</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.512246154597482</v>
+        <v>1.602440792499997</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.07383690275453292</v>
+        <v>0.1470891418328584</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.69219672016963</v>
+        <v>3.824752346922065</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830332</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.676708399916691</v>
+        <v>-5.451221805160403</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.62766313424097</v>
+        <v>1.717857772143485</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.07383690275453292</v>
+        <v>0.1470891418328584</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.854400776868673</v>
+        <v>3.986956403621108</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.761426342137644</v>
+        <v>-5.535939747381356</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.588622595316403</v>
+        <v>1.678817233218918</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1589529316825793</v>
+        <v>0.061973112904812</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.79817779747566</v>
+        <v>3.930733424228094</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586815</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.843361160406527</v>
+        <v>-5.617874565650239</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.56607808557734</v>
+        <v>1.656272723479856</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1688876772696595</v>
+        <v>0.05203836731773182</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.802446367691903</v>
+        <v>3.935001994444338</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.945337282654934</v>
+        <v>-5.719850687898647</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.53421327513388</v>
+        <v>1.624407913036395</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.270863799518067</v>
+        <v>-0.04993775493067576</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.750186332798761</v>
+        <v>3.882741959551196</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.835330999177713</v>
+        <v>-5.609844404421425</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.570368675768944</v>
+        <v>1.660563313671459</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2476592276007918</v>
+        <v>-0.02673318301340055</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.756261963193301</v>
+        <v>3.888817589945736</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818526</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.692271423436788</v>
+        <v>-5.466784828680499</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.631842516787288</v>
+        <v>1.722037154689804</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2396458010108126</v>
+        <v>-0.01871975642342127</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.765320029869263</v>
+        <v>3.897875656621698</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051791</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.39082469796495</v>
+        <v>-5.165338103208661</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.759682089858559</v>
+        <v>1.849876727761075</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.0618009244610247</v>
+        <v>0.282726969048416</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.953448948034902</v>
+        <v>4.086004574787337</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679628</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.415414942200134</v>
+        <v>-5.189928347443845</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.750817169917196</v>
+        <v>1.841011807819712</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.0618009244610247</v>
+        <v>0.282726969048416</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.954420125787612</v>
+        <v>4.086975752540047</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474163</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.364376566193614</v>
+        <v>-5.138889971437325</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.77207542469956</v>
+        <v>1.862270062602075</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.0618009244610247</v>
+        <v>0.282726969048416</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.955263030167368</v>
+        <v>4.087818656919803</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969547</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.323237271326983</v>
+        <v>-5.097750676570694</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.807569241520357</v>
+        <v>1.897763879422873</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1029402193276555</v>
+        <v>0.3238662639150468</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.998984705961491</v>
+        <v>4.131540332713926</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700483</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.212631131247381</v>
+        <v>-4.987144536491092</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.667995693676133</v>
+        <v>1.758190331578648</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2135463594072575</v>
+        <v>0.4344724039946488</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.881532386133187</v>
+        <v>4.014088012885622</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077645</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.343211865778223</v>
+        <v>-5.117725271021935</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.619265443937759</v>
+        <v>1.709460081840275</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.08296562487641501</v>
+        <v>0.3038916694638063</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.806685989488645</v>
+        <v>3.93924161624108</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.178715531587262</v>
+        <v>-4.953228936830973</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.669490796690227</v>
+        <v>1.759685434592742</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.08296562487641501</v>
+        <v>0.3038916694638063</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.791112808564728</v>
+        <v>3.923668435317163</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077631</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.206085464271694</v>
+        <v>-4.980598869515405</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.657730534052884</v>
+        <v>1.747925171955399</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.08296562487641501</v>
+        <v>0.3038916694638063</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.790300519001157</v>
+        <v>3.922856145753593</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147912</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.216470659161583</v>
+        <v>-4.990984064405295</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.663445235222</v>
+        <v>1.753639873124516</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.0725804299865257</v>
+        <v>0.293506474573917</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.793938181192297</v>
+        <v>3.926493807944731</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735286</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.235058817883808</v>
+        <v>-5.009572223127519</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.726846977509535</v>
+        <v>1.817041615412051</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.05399227126430034</v>
+        <v>0.2749183158516916</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.853622291735386</v>
+        <v>3.986177918487821</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496557</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.235357364579844</v>
+        <v>-5.009870769823555</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.723596569649419</v>
+        <v>1.813791207551935</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.05399227126430034</v>
+        <v>0.2749183158516916</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.850491302553685</v>
+        <v>3.98304692930612</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108862</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.134534230889416</v>
+        <v>-4.909047636133128</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.768456718064982</v>
+        <v>1.858651355967498</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.06645648674865418</v>
+        <v>0.2873825313360455</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.862500726783689</v>
+        <v>3.995056353536123</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121471</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.943752870137009</v>
+        <v>-4.718266275380721</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.844898515844488</v>
+        <v>1.935093153747004</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2572378475010615</v>
+        <v>0.4781638920884528</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.977098796713676</v>
+        <v>4.109654423466111</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906084</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.925236016095189</v>
+        <v>-4.6997494213389</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.832142103198813</v>
+        <v>1.922336741101328</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.2701679769262698</v>
+        <v>0.491094021513661</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.964693720106398</v>
+        <v>4.097249346858833</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.900042831593871</v>
+        <v>-4.674556236837582</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.877186313611398</v>
+        <v>1.967380951513914</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.2953611614275881</v>
+        <v>0.5162872060149793</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.014776567419247</v>
+        <v>4.147332194171682</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539898</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.887988704680908</v>
+        <v>-4.66250210992462</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.875694532278021</v>
+        <v>1.965889170180537</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.3074152883405509</v>
+        <v>0.5283413329279422</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.015695611468463</v>
+        <v>4.148251238220897</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.894611951371266</v>
+        <v>-4.669125356614978</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.874925863786014</v>
+        <v>1.96512050168853</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.3007920416501926</v>
+        <v>0.5217180862375839</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.013602293638384</v>
+        <v>4.146157920390818</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382923</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.791731361842674</v>
+        <v>-4.566244767086385</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.928929125475333</v>
+        <v>2.019123763377849</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4036726311787855</v>
+        <v>0.6245986757661768</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.088181673233422</v>
+        <v>4.220737299985856</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760319</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.81517340102276</v>
+        <v>-4.589686806266472</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.939754979976893</v>
+        <v>2.029949617879408</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4036726311787855</v>
+        <v>0.6245986757661768</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.108384343407016</v>
+        <v>4.240939970159451</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781709</v>
+        <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.833245909314372</v>
+        <v>-4.607759314558083</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.932525976660248</v>
+        <v>2.022720614562764</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4036726311787855</v>
+        <v>0.6245986757661768</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.108384343407016</v>
+        <v>4.240939970159451</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082838</v>
+        <v>3.670068888082833</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.064419703191004</v>
+        <v>-4.838933108434715</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.800308372703062</v>
+        <v>1.890503010605578</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4036726311787855</v>
+        <v>0.6245986757661768</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.068636257000483</v>
+        <v>4.201191883752918</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943589</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.033133682650549</v>
+        <v>-4.80764708789426</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.819845399916184</v>
+        <v>1.9100400378187</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4349586517192409</v>
+        <v>0.6558846963066322</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.094430488321696</v>
+        <v>4.226986115074131</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677827</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.880108290537264</v>
+        <v>-4.654621695780976</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.980226556334402</v>
+        <v>2.070421194236918</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.587984043832525</v>
+        <v>0.8089100884199163</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.28541672316257</v>
+        <v>4.417972349915005</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073886</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.887245361722555</v>
+        <v>-4.661758766966266</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.164837952768578</v>
+        <v>2.255032590671094</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.587984043832525</v>
+        <v>0.8089100884199163</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.472882948070863</v>
+        <v>4.605438574823298</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.668347396350242</v>
+        <v>3.779080946201502</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.75827766603951</v>
+        <v>-4.745712084090071</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.185827982395878</v>
+        <v>2.190854215175654</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7169517395155697</v>
+        <v>0.7647515485600713</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.519666516834771</v>
+        <v>4.548346402261473</v>
       </c>
     </row>
   </sheetData>
